--- a/Thread Chart/Gemline Thread Charts.xlsx
+++ b/Thread Chart/Gemline Thread Charts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\fs1\InformationManagement\Procedures &amp; References\Embroidery Thread Charts\Completed\Gemline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B643129-8CBC-4AEC-A798-C7EFC1BF30E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2605AE4C-B04C-406F-8861-BDB3BD16F151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22920" yWindow="-1095" windowWidth="29040" windowHeight="15840" xr2:uid="{F028543A-CA1A-4C22-838B-894A262A5CAB}"/>
+    <workbookView xWindow="19090" yWindow="-5720" windowWidth="38620" windowHeight="21100" xr2:uid="{F028543A-CA1A-4C22-838B-894A262A5CAB}"/>
   </bookViews>
   <sheets>
     <sheet name="Robison Anton SS Rayon" sheetId="7" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Robinson Anton Super Brite'!$A$1:$I$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Robison Anton SS Rayon'!$A$1:$I$322</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,6 +31,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -52,6 +55,9 @@
     <t>Thread Number</t>
   </si>
   <si>
+    <t>Monitor Display Color</t>
+  </si>
+  <si>
     <t>PMS Number</t>
   </si>
   <si>
@@ -64,1096 +70,1093 @@
     <t>B</t>
   </si>
   <si>
-    <t>Monitor Display Color</t>
+    <t>Ice Blue</t>
+  </si>
+  <si>
+    <t>Blues</t>
+  </si>
+  <si>
+    <t>RA SSR 9</t>
+  </si>
+  <si>
+    <t>Cadet Blue</t>
+  </si>
+  <si>
+    <t>Paris Blue</t>
+  </si>
+  <si>
+    <t>Heron Blue</t>
+  </si>
+  <si>
+    <t>Pastel blue</t>
+  </si>
+  <si>
+    <t>Cristy Blue</t>
+  </si>
+  <si>
+    <t>Sky Blue</t>
+  </si>
+  <si>
+    <t>Blue Frost</t>
+  </si>
+  <si>
+    <t>Country Blue</t>
+  </si>
+  <si>
+    <t>Blue Horizon</t>
+  </si>
+  <si>
+    <t>Tropic Blue</t>
+  </si>
+  <si>
+    <t>Ultra Blue</t>
+  </si>
+  <si>
+    <t>Bridgeport Blue</t>
+  </si>
+  <si>
+    <t>Baby Blue</t>
+  </si>
+  <si>
+    <t>Lake blue</t>
+  </si>
+  <si>
+    <t>Periwinkle</t>
+  </si>
+  <si>
+    <t>Indian Ocean</t>
+  </si>
+  <si>
+    <t>Misty</t>
+  </si>
+  <si>
+    <t>Pro Saxon</t>
+  </si>
+  <si>
+    <t>Pro Twinkle</t>
+  </si>
+  <si>
+    <t>Aquamarine</t>
+  </si>
+  <si>
+    <t>Caribbean Blue</t>
+  </si>
+  <si>
+    <t>Copen</t>
+  </si>
+  <si>
+    <t>Bright Blue</t>
+  </si>
+  <si>
+    <t>Atlantis Blue</t>
+  </si>
+  <si>
+    <t>Pro Lusty Blue</t>
+  </si>
+  <si>
+    <t>Jay Blue</t>
+  </si>
+  <si>
+    <t>Surf Blue</t>
+  </si>
+  <si>
+    <t>California Blue</t>
+  </si>
+  <si>
+    <t>Pacific Blue</t>
+  </si>
+  <si>
+    <t>Boo Boo Blue</t>
+  </si>
+  <si>
+    <t>Solar Blue</t>
+  </si>
+  <si>
+    <t>Ozone</t>
+  </si>
+  <si>
+    <t>Wonder Blue</t>
+  </si>
+  <si>
+    <t>Blue</t>
+  </si>
+  <si>
+    <t>Sapphire</t>
+  </si>
+  <si>
+    <t>Slate Blue</t>
+  </si>
+  <si>
+    <t>Pro Peacock</t>
+  </si>
+  <si>
+    <t>Pro Imperial</t>
+  </si>
+  <si>
+    <t>China Blue</t>
+  </si>
+  <si>
+    <t>Imperial Blue</t>
+  </si>
+  <si>
+    <t>Soldier Blue</t>
+  </si>
+  <si>
+    <t>Pro Brilliance</t>
+  </si>
+  <si>
+    <t>Blue Suede</t>
+  </si>
+  <si>
+    <t>Jamie Blue</t>
+  </si>
+  <si>
+    <t>Empire Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Royal </t>
+  </si>
+  <si>
+    <t>Pro Midnight</t>
+  </si>
+  <si>
+    <t>Ash</t>
+  </si>
+  <si>
+    <t>Light Midnight</t>
+  </si>
+  <si>
+    <t>Blue Ink</t>
+  </si>
+  <si>
+    <t>Pro Dark Blue</t>
+  </si>
+  <si>
+    <t>Salem Blue</t>
+  </si>
+  <si>
+    <t>Pro Navy</t>
+  </si>
+  <si>
+    <t>Flag Blue</t>
+  </si>
+  <si>
+    <t>Th Navy</t>
+  </si>
+  <si>
+    <t>Smokey</t>
+  </si>
+  <si>
+    <t>7547C</t>
+  </si>
+  <si>
+    <t>Natural White</t>
+  </si>
+  <si>
+    <t>Browns</t>
+  </si>
+  <si>
+    <t>Aspen White</t>
+  </si>
+  <si>
+    <t>Ivory</t>
+  </si>
+  <si>
+    <t>Bone</t>
+  </si>
+  <si>
+    <t>Ecru</t>
+  </si>
+  <si>
+    <t>Cottage Beige</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>Seashell</t>
+  </si>
+  <si>
+    <t>Amber Beige</t>
+  </si>
+  <si>
+    <t>Platinum</t>
+  </si>
+  <si>
+    <t>Tan</t>
+  </si>
+  <si>
+    <t>Pro Beige</t>
   </si>
   <si>
     <t>Yellows</t>
   </si>
   <si>
+    <t>Mocha Cream</t>
+  </si>
+  <si>
+    <t>Bamboo</t>
+  </si>
+  <si>
+    <t>Perfect Tan</t>
+  </si>
+  <si>
+    <t>Ashley Gold</t>
+  </si>
+  <si>
+    <t>Topaz</t>
+  </si>
+  <si>
+    <t>Wicker</t>
+  </si>
+  <si>
+    <t>Lt. Bronze</t>
+  </si>
+  <si>
+    <t>Rattan</t>
+  </si>
+  <si>
+    <t>Almond</t>
+  </si>
+  <si>
+    <t>Mushroom</t>
+  </si>
+  <si>
+    <t>Copper</t>
+  </si>
+  <si>
+    <t>Toast</t>
+  </si>
+  <si>
+    <t>Pro Brown</t>
+  </si>
+  <si>
+    <t>Cocoa Mulch</t>
+  </si>
+  <si>
+    <t>Hazel</t>
+  </si>
+  <si>
+    <t>Dark Rust</t>
+  </si>
+  <si>
+    <t>Sand Dune</t>
+  </si>
+  <si>
+    <t>Earthen Tan</t>
+  </si>
+  <si>
+    <t>Lt. Cocoa</t>
+  </si>
+  <si>
+    <t>Pro Walnut</t>
+  </si>
+  <si>
+    <t>Chocolate</t>
+  </si>
+  <si>
+    <t>Sienna</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Dogwood</t>
+  </si>
+  <si>
+    <t>Coffee Bean</t>
+  </si>
+  <si>
+    <t>Dark Taupe</t>
+  </si>
+  <si>
+    <t>Dark Brown</t>
+  </si>
+  <si>
+    <t>Espresso</t>
+  </si>
+  <si>
+    <t>Egyptian Brown</t>
+  </si>
+  <si>
+    <t>Steel Gray</t>
+  </si>
+  <si>
+    <t>Grays</t>
+  </si>
+  <si>
+    <t>Silver Steel</t>
+  </si>
+  <si>
+    <t>Steel</t>
+  </si>
+  <si>
+    <t>CG1</t>
+  </si>
+  <si>
+    <t>Chrome</t>
+  </si>
+  <si>
+    <t>Oyster</t>
+  </si>
+  <si>
+    <t>Gray</t>
+  </si>
+  <si>
+    <t>Skylight</t>
+  </si>
+  <si>
+    <t>Saturn Gray</t>
+  </si>
+  <si>
+    <t>Dover Gray</t>
+  </si>
+  <si>
+    <t>Traditional Gray</t>
+  </si>
+  <si>
+    <t>Stainless Steel</t>
+  </si>
+  <si>
+    <t>Storm Gray</t>
+  </si>
+  <si>
+    <t>Pro Cool Gray</t>
+  </si>
+  <si>
+    <t>Pro Pearl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud </t>
+  </si>
+  <si>
+    <t>Pro Night Sky</t>
+  </si>
+  <si>
+    <t>Gray Rod</t>
+  </si>
+  <si>
+    <t>Pro Gray</t>
+  </si>
+  <si>
+    <t>Pewter</t>
+  </si>
+  <si>
+    <t>Twilight</t>
+  </si>
+  <si>
+    <t>Black Chrome</t>
+  </si>
+  <si>
+    <t>Black 7</t>
+  </si>
+  <si>
+    <t>Celery</t>
+  </si>
+  <si>
+    <t>Greens</t>
+  </si>
+  <si>
+    <t>Pastel Green</t>
+  </si>
+  <si>
+    <t>Mint</t>
+  </si>
+  <si>
+    <t>Sea Mist</t>
+  </si>
+  <si>
+    <t>Seafrost</t>
+  </si>
+  <si>
+    <t>Pebblestone</t>
+  </si>
+  <si>
+    <t>Green Oak</t>
+  </si>
+  <si>
+    <t>Flite Green</t>
+  </si>
+  <si>
+    <t>Palm Leaf</t>
+  </si>
+  <si>
+    <t>Nile</t>
+  </si>
+  <si>
+    <t>Sun Shadow</t>
+  </si>
+  <si>
+    <t>Peapod</t>
+  </si>
+  <si>
+    <t>Aqua Pearl</t>
+  </si>
+  <si>
+    <t>Spring Garden</t>
+  </si>
+  <si>
+    <t>Erin Green</t>
+  </si>
+  <si>
+    <t>Turquoise</t>
+  </si>
+  <si>
+    <t>Wintergreen</t>
+  </si>
+  <si>
+    <t>Moss</t>
+  </si>
+  <si>
+    <t>Green Dust</t>
+  </si>
+  <si>
+    <t>Emerald</t>
+  </si>
+  <si>
+    <t>Spruce</t>
+  </si>
+  <si>
+    <t>J Turquoise</t>
+  </si>
+  <si>
+    <t>Bluestone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">         </t>
+  </si>
+  <si>
+    <t>Meadow</t>
+  </si>
+  <si>
+    <t>Tamarack</t>
+  </si>
+  <si>
+    <t>Crescent Moon</t>
+  </si>
+  <si>
+    <t>Jungle Green</t>
+  </si>
+  <si>
+    <t>Newport</t>
+  </si>
+  <si>
+    <t>Harvest</t>
+  </si>
+  <si>
+    <t>Foliage Green</t>
+  </si>
+  <si>
+    <t>Pro Erin</t>
+  </si>
+  <si>
+    <t>Green Grass</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>Autumn Green</t>
+  </si>
+  <si>
+    <t>Isle Green</t>
+  </si>
+  <si>
+    <t>Olive</t>
+  </si>
+  <si>
+    <t>Water Lilly</t>
+  </si>
+  <si>
+    <t>Pro Teal</t>
+  </si>
+  <si>
+    <t>Teal</t>
+  </si>
+  <si>
+    <t>Willow</t>
+  </si>
+  <si>
+    <t>Pine Green</t>
+  </si>
+  <si>
+    <t>Kelly</t>
+  </si>
+  <si>
+    <t>Cypress</t>
+  </si>
+  <si>
+    <t>Palmetto</t>
+  </si>
+  <si>
+    <t>Desert Cactus</t>
+  </si>
+  <si>
+    <t>Olive Drab</t>
+  </si>
+  <si>
+    <t>Sage</t>
+  </si>
+  <si>
+    <t>Deep Green</t>
+  </si>
+  <si>
+    <t>Pro Hunter</t>
+  </si>
+  <si>
+    <t>Fleece Green</t>
+  </si>
+  <si>
+    <t>Green Bay</t>
+  </si>
+  <si>
+    <t>TH Green</t>
+  </si>
+  <si>
+    <t>Evergreen</t>
+  </si>
+  <si>
+    <t>Holly</t>
+  </si>
+  <si>
+    <t>Harbor Green</t>
+  </si>
+  <si>
+    <t>Blue Spruce</t>
+  </si>
+  <si>
+    <t>Dress Green</t>
+  </si>
+  <si>
+    <t>Pro Green</t>
+  </si>
+  <si>
+    <t>Ivy</t>
+  </si>
+  <si>
+    <t>Dark Army Green</t>
+  </si>
+  <si>
+    <t>Hedge</t>
+  </si>
+  <si>
+    <t>Green Petal</t>
+  </si>
+  <si>
+    <t>Lizzy Lime</t>
+  </si>
+  <si>
+    <t>Pro Dark Green</t>
+  </si>
+  <si>
+    <t>Green Sail</t>
+  </si>
+  <si>
+    <t>Dark Teal</t>
+  </si>
+  <si>
+    <t>D.H. Green</t>
+  </si>
+  <si>
+    <t>Army Green</t>
+  </si>
+  <si>
+    <t>Pumpkin</t>
+  </si>
+  <si>
     <t>Oranges</t>
   </si>
   <si>
+    <t>Golden Poppy</t>
+  </si>
+  <si>
+    <t>Dark Tex Orange</t>
+  </si>
+  <si>
+    <t>Paprika</t>
+  </si>
+  <si>
+    <t>Tex Orange</t>
+  </si>
+  <si>
+    <t>Sun Orange</t>
+  </si>
+  <si>
+    <t>Rust</t>
+  </si>
+  <si>
+    <t>Saffron</t>
+  </si>
+  <si>
+    <t>Honeysuckle</t>
+  </si>
+  <si>
+    <t>Old DK Tex Orange</t>
+  </si>
+  <si>
+    <t>Petal Pink</t>
+  </si>
+  <si>
+    <t>Pinks</t>
+  </si>
+  <si>
+    <t>Opaline</t>
+  </si>
+  <si>
+    <t>475C</t>
+  </si>
+  <si>
+    <t>Flesh</t>
+  </si>
+  <si>
+    <t>Light Pink</t>
+  </si>
+  <si>
+    <t>Peach</t>
+  </si>
+  <si>
+    <t>Tawny</t>
+  </si>
+  <si>
+    <t>Pink</t>
+  </si>
+  <si>
+    <t>Emily Pink</t>
+  </si>
+  <si>
+    <t>Pink Mist</t>
+  </si>
+  <si>
+    <t>Rose</t>
+  </si>
+  <si>
+    <t>Dusty Rose</t>
+  </si>
+  <si>
+    <t>Rose Cerise</t>
+  </si>
+  <si>
+    <t>Salmon</t>
+  </si>
+  <si>
+    <t>501C</t>
+  </si>
+  <si>
+    <t>Melon</t>
+  </si>
+  <si>
+    <t>Coral</t>
+  </si>
+  <si>
+    <t>Wild Pink</t>
+  </si>
+  <si>
+    <t>Rose Tint</t>
+  </si>
+  <si>
+    <t>Floral Pink</t>
+  </si>
+  <si>
+    <t>Primrose</t>
+  </si>
+  <si>
+    <t>Bitteroot</t>
+  </si>
+  <si>
+    <t>Bashful Pink</t>
+  </si>
+  <si>
+    <t>Strawberry</t>
+  </si>
+  <si>
+    <t>Rhodamine</t>
+  </si>
+  <si>
+    <t>Ruby Glint</t>
+  </si>
+  <si>
+    <t>Hot Pink</t>
+  </si>
+  <si>
+    <t>Pro Cinnamon</t>
+  </si>
+  <si>
+    <t>Persimmon</t>
+  </si>
+  <si>
+    <t>Azalea</t>
+  </si>
+  <si>
+    <t>Crimson</t>
+  </si>
+  <si>
+    <t>Hot Peony</t>
+  </si>
+  <si>
+    <t>Cabernet</t>
+  </si>
+  <si>
+    <t>Passion Rose</t>
+  </si>
+  <si>
+    <t>New Berry</t>
+  </si>
+  <si>
+    <t>Cherry Stone</t>
+  </si>
+  <si>
+    <t>Perfect Ruby</t>
+  </si>
+  <si>
+    <t>Brushed Burgundy</t>
+  </si>
+  <si>
+    <t>Violet</t>
+  </si>
+  <si>
+    <t>Purples</t>
+  </si>
+  <si>
+    <t>Lavender</t>
+  </si>
+  <si>
+    <t>Mid Lilac</t>
+  </si>
+  <si>
+    <t>Tulip</t>
+  </si>
+  <si>
+    <t>Plum</t>
+  </si>
+  <si>
+    <t>Mauve</t>
+  </si>
+  <si>
+    <t>Sterling</t>
+  </si>
+  <si>
+    <t>Iris</t>
+  </si>
+  <si>
+    <t>Laurie Lilac</t>
+  </si>
+  <si>
+    <t>Cachet</t>
+  </si>
+  <si>
+    <t>Plum Wine</t>
+  </si>
+  <si>
+    <t>Raspberry</t>
+  </si>
+  <si>
+    <t>Mulberry</t>
+  </si>
+  <si>
+    <t>Ducky Mauve</t>
+  </si>
+  <si>
+    <t>Purple Shadow</t>
+  </si>
+  <si>
+    <t>Purple</t>
+  </si>
+  <si>
+    <t>Dark Purple</t>
+  </si>
+  <si>
+    <t>Purple Twist</t>
+  </si>
+  <si>
+    <t>Violet Blue</t>
+  </si>
+  <si>
+    <t>Purple Maze</t>
+  </si>
+  <si>
+    <t>Purple Accent</t>
+  </si>
+  <si>
+    <t>Pro Brite Star</t>
+  </si>
+  <si>
+    <t>Pro Violet</t>
+  </si>
+  <si>
+    <t>Pro Purple</t>
+  </si>
+  <si>
+    <t>Port Wine</t>
+  </si>
+  <si>
+    <t>Pro Maroon</t>
+  </si>
+  <si>
+    <t>Rosewood</t>
+  </si>
+  <si>
     <t>Reds</t>
   </si>
   <si>
-    <t>Pinks</t>
-  </si>
-  <si>
-    <t>Purples</t>
-  </si>
-  <si>
-    <t>Blues</t>
-  </si>
-  <si>
-    <t>Greens</t>
-  </si>
-  <si>
-    <t>Browns</t>
-  </si>
-  <si>
-    <t>Grays</t>
+    <t>Lipstick</t>
+  </si>
+  <si>
+    <t>Tuxedo Red</t>
+  </si>
+  <si>
+    <t>Foxy Red</t>
+  </si>
+  <si>
+    <t>Antique Red</t>
+  </si>
+  <si>
+    <t>Jockey Red</t>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <t>Very Red</t>
+  </si>
+  <si>
+    <t>Scarlet</t>
+  </si>
+  <si>
+    <t>Wildfire</t>
+  </si>
+  <si>
+    <t>Candy Apple Red</t>
+  </si>
+  <si>
+    <t>Red Berry</t>
+  </si>
+  <si>
+    <t>Auburn</t>
+  </si>
+  <si>
+    <t>Pro Red</t>
+  </si>
+  <si>
+    <t>Cranberry</t>
+  </si>
+  <si>
+    <t>Burgundy</t>
+  </si>
+  <si>
+    <t>Red Jubilee</t>
+  </si>
+  <si>
+    <t>Terra Cotta</t>
+  </si>
+  <si>
+    <t>Th Burgundy</t>
+  </si>
+  <si>
+    <t>Russet</t>
+  </si>
+  <si>
+    <t>Carolina Red</t>
+  </si>
+  <si>
+    <t>Wine</t>
+  </si>
+  <si>
+    <t>Pro Firebrand</t>
+  </si>
+  <si>
+    <t>Dark Maroon</t>
+  </si>
+  <si>
+    <t>Warm Wine</t>
+  </si>
+  <si>
+    <t>Eggshell</t>
+  </si>
+  <si>
+    <t>Light Maize</t>
+  </si>
+  <si>
+    <t>Pro Maize</t>
+  </si>
+  <si>
+    <t>Maize</t>
+  </si>
+  <si>
+    <t>Pale Yellow</t>
+  </si>
+  <si>
+    <t>Lemon</t>
+  </si>
+  <si>
+    <t>Daffodil</t>
+  </si>
+  <si>
+    <t>Marine Gold</t>
+  </si>
+  <si>
+    <t>Glow</t>
+  </si>
+  <si>
+    <t>Canary Yellow</t>
+  </si>
+  <si>
+    <t>Moonbeam</t>
+  </si>
+  <si>
+    <t>Sunflower</t>
+  </si>
+  <si>
+    <t>Goldenlite</t>
+  </si>
+  <si>
+    <t>Honey</t>
+  </si>
+  <si>
+    <t>Star Gold</t>
+  </si>
+  <si>
+    <t>Goldenrod</t>
+  </si>
+  <si>
+    <t>Marigold</t>
+  </si>
+  <si>
+    <t>Pro Gold</t>
+  </si>
+  <si>
+    <t>Manila</t>
+  </si>
+  <si>
+    <t>Scholastic</t>
+  </si>
+  <si>
+    <t>Buttercup</t>
+  </si>
+  <si>
+    <t>Bright Yellow</t>
+  </si>
+  <si>
+    <t>Mustard</t>
+  </si>
+  <si>
+    <t>Merit Gold</t>
+  </si>
+  <si>
+    <t>Penny</t>
+  </si>
+  <si>
+    <t>Yellow</t>
+  </si>
+  <si>
+    <t>Nectar</t>
+  </si>
+  <si>
+    <t>Yellow Mist</t>
+  </si>
+  <si>
+    <t>TH Gold</t>
+  </si>
+  <si>
+    <t>14 Kt. Gold</t>
+  </si>
+  <si>
+    <t>Shimmering Gold</t>
+  </si>
+  <si>
+    <t>Black Eyed Susie</t>
+  </si>
+  <si>
+    <t>Old Gold</t>
+  </si>
+  <si>
+    <t>Sun Gold</t>
+  </si>
+  <si>
+    <t>Pollen Gold</t>
+  </si>
+  <si>
+    <t>Ginger</t>
+  </si>
+  <si>
+    <t>Bullion</t>
+  </si>
+  <si>
+    <t>24 Kt. Gold</t>
+  </si>
+  <si>
+    <t>SBP-9</t>
+  </si>
+  <si>
+    <t>Dolphin Blue</t>
+  </si>
+  <si>
+    <t>Rockport Blue</t>
+  </si>
+  <si>
+    <t>Mountainview</t>
+  </si>
+  <si>
+    <t>Light Navy</t>
+  </si>
+  <si>
+    <t>PN Navy</t>
+  </si>
+  <si>
+    <t>Midnight Navy</t>
+  </si>
+  <si>
+    <t>Navy</t>
+  </si>
+  <si>
+    <t>Golden Tan</t>
+  </si>
+  <si>
+    <t>Beige</t>
+  </si>
+  <si>
+    <t>Brown</t>
+  </si>
+  <si>
+    <t>Cinder</t>
+  </si>
+  <si>
+    <t>Gray Flannel</t>
+  </si>
+  <si>
+    <t>Vassar Chic</t>
   </si>
   <si>
     <t>Cool Gray 10</t>
   </si>
   <si>
-    <t>Blue</t>
-  </si>
-  <si>
-    <t>Brown</t>
-  </si>
-  <si>
-    <t>Gray</t>
-  </si>
-  <si>
-    <t>Green</t>
-  </si>
-  <si>
-    <t>Pink</t>
-  </si>
-  <si>
-    <t>Purple</t>
-  </si>
-  <si>
-    <t>Red</t>
-  </si>
-  <si>
-    <t>Yellow</t>
-  </si>
-  <si>
-    <t>Platinum</t>
-  </si>
-  <si>
-    <t>Chrome</t>
-  </si>
-  <si>
-    <t>Copper</t>
-  </si>
-  <si>
-    <t>Coral</t>
-  </si>
-  <si>
-    <t>Emerald</t>
-  </si>
-  <si>
-    <t>Turquoise</t>
-  </si>
-  <si>
-    <t>Aquamarine</t>
-  </si>
-  <si>
-    <t>Sapphire</t>
-  </si>
-  <si>
-    <t>Black 7</t>
-  </si>
-  <si>
-    <t>Old Gold</t>
-  </si>
-  <si>
-    <t>SBP-9</t>
-  </si>
-  <si>
-    <t>Olive</t>
-  </si>
-  <si>
-    <t>Gold</t>
-  </si>
-  <si>
-    <t>Dark Rust</t>
-  </si>
-  <si>
-    <t>Baby Blue</t>
-  </si>
-  <si>
-    <t>Nile</t>
-  </si>
-  <si>
-    <t>Sun Gold</t>
-  </si>
-  <si>
-    <t>Navy</t>
-  </si>
-  <si>
-    <t>Marigold</t>
-  </si>
-  <si>
-    <t>Twilight</t>
-  </si>
-  <si>
-    <t>Scarlet</t>
-  </si>
-  <si>
-    <t>Willow</t>
-  </si>
-  <si>
-    <t>Beige</t>
-  </si>
-  <si>
-    <t>Wine</t>
-  </si>
-  <si>
-    <t>Meadow</t>
-  </si>
-  <si>
-    <t>Chocolate</t>
-  </si>
-  <si>
-    <t>Palmetto</t>
-  </si>
-  <si>
-    <t>Tamarack</t>
-  </si>
-  <si>
-    <t>Toast</t>
-  </si>
-  <si>
-    <t>Ecru</t>
-  </si>
-  <si>
-    <t>Lipstick</t>
-  </si>
-  <si>
-    <t>Glow</t>
-  </si>
-  <si>
-    <t>Paprika</t>
-  </si>
-  <si>
-    <t>Mint</t>
-  </si>
-  <si>
-    <t>Sky Blue</t>
-  </si>
-  <si>
-    <t>Kelly</t>
-  </si>
-  <si>
-    <t>Palm Leaf</t>
-  </si>
-  <si>
-    <t>Goldenrod</t>
-  </si>
-  <si>
-    <t>Light Pink</t>
-  </si>
-  <si>
-    <t>Rose Cerise</t>
-  </si>
-  <si>
-    <t>Copen</t>
-  </si>
-  <si>
-    <t>Honey</t>
-  </si>
-  <si>
-    <t>Burgundy</t>
-  </si>
-  <si>
-    <t>Russet</t>
-  </si>
-  <si>
-    <t>Tawny</t>
-  </si>
-  <si>
-    <t>Wild Pink</t>
-  </si>
-  <si>
-    <t>Hot Pink</t>
-  </si>
-  <si>
-    <t>Ruby Glint</t>
-  </si>
-  <si>
-    <t>Foxy Red</t>
-  </si>
-  <si>
-    <t>Maize</t>
-  </si>
-  <si>
     <t>Charcoal</t>
   </si>
   <si>
     <t>Warm Gray 11</t>
   </si>
   <si>
+    <t>Limerick</t>
+  </si>
+  <si>
+    <t>Pastoral Green</t>
+  </si>
+  <si>
+    <t>Neon Green</t>
+  </si>
+  <si>
+    <t>M.D. Green</t>
+  </si>
+  <si>
+    <t>Connor Green</t>
+  </si>
+  <si>
+    <t>Oceanic Green</t>
+  </si>
+  <si>
+    <t>Dark Texas Orange</t>
+  </si>
+  <si>
     <t>Radiant Red</t>
-  </si>
-  <si>
-    <t>Carolina Red</t>
-  </si>
-  <si>
-    <t>Cranberry</t>
-  </si>
-  <si>
-    <t>Tan</t>
-  </si>
-  <si>
-    <t>Steel Gray</t>
-  </si>
-  <si>
-    <t>Slate Blue</t>
-  </si>
-  <si>
-    <t>Moss</t>
-  </si>
-  <si>
-    <t>Spruce</t>
-  </si>
-  <si>
-    <t>Jockey Red</t>
-  </si>
-  <si>
-    <t>Paris Blue</t>
-  </si>
-  <si>
-    <t>Deep Green</t>
-  </si>
-  <si>
-    <t>Violet</t>
-  </si>
-  <si>
-    <t>Tulip</t>
-  </si>
-  <si>
-    <t>Mauve</t>
-  </si>
-  <si>
-    <t>Iris</t>
-  </si>
-  <si>
-    <t>Rust</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Plum</t>
-  </si>
-  <si>
-    <t>Melon</t>
-  </si>
-  <si>
-    <t>Salmon</t>
-  </si>
-  <si>
-    <t>Ice Blue</t>
-  </si>
-  <si>
-    <t>Imperial Blue</t>
-  </si>
-  <si>
-    <t>Light Navy</t>
-  </si>
-  <si>
-    <t>Misty</t>
-  </si>
-  <si>
-    <t>Teal</t>
-  </si>
-  <si>
-    <t>Isle Green</t>
-  </si>
-  <si>
-    <t>Evergreen</t>
-  </si>
-  <si>
-    <t>Celery</t>
-  </si>
-  <si>
-    <t>Olive Drab</t>
-  </si>
-  <si>
-    <t>Green Oak</t>
-  </si>
-  <si>
-    <t>Erin Green</t>
-  </si>
-  <si>
-    <t>Pastoral Green</t>
-  </si>
-  <si>
-    <t>Holly</t>
-  </si>
-  <si>
-    <t>Lemon</t>
-  </si>
-  <si>
-    <t>Daffodil</t>
-  </si>
-  <si>
-    <t>Saffron</t>
-  </si>
-  <si>
-    <t>Golden Poppy</t>
-  </si>
-  <si>
-    <t>Mustard</t>
-  </si>
-  <si>
-    <t>Penny</t>
-  </si>
-  <si>
-    <t>Ginger</t>
-  </si>
-  <si>
-    <t>Terra Cotta</t>
-  </si>
-  <si>
-    <t>Ivory</t>
-  </si>
-  <si>
-    <t>Amber Beige</t>
-  </si>
-  <si>
-    <t>Espresso</t>
-  </si>
-  <si>
-    <t>Bamboo</t>
-  </si>
-  <si>
-    <t>Coffee Bean</t>
-  </si>
-  <si>
-    <t>Ash</t>
-  </si>
-  <si>
-    <t>Natural White</t>
-  </si>
-  <si>
-    <t>Eggshell</t>
-  </si>
-  <si>
-    <t>Dark Brown</t>
-  </si>
-  <si>
-    <t>Dusty Rose</t>
-  </si>
-  <si>
-    <t>Dark Purple</t>
-  </si>
-  <si>
-    <t>Cristy Blue</t>
-  </si>
-  <si>
-    <t>Jay Blue</t>
-  </si>
-  <si>
-    <t>Jamie Blue</t>
-  </si>
-  <si>
-    <t>Light Midnight</t>
-  </si>
-  <si>
-    <t>Midnight Navy</t>
-  </si>
-  <si>
-    <t>California Blue</t>
-  </si>
-  <si>
-    <t>Pine Green</t>
-  </si>
-  <si>
-    <t>Harbor Green</t>
-  </si>
-  <si>
-    <t>Sea Mist</t>
-  </si>
-  <si>
-    <t>Topaz</t>
-  </si>
-  <si>
-    <t>Ashley Gold</t>
-  </si>
-  <si>
-    <t>Sienna</t>
-  </si>
-  <si>
-    <t>Oyster</t>
-  </si>
-  <si>
-    <t>Cinder</t>
-  </si>
-  <si>
-    <t>Dover Gray</t>
-  </si>
-  <si>
-    <t>Sterling</t>
-  </si>
-  <si>
-    <t>Star Gold</t>
-  </si>
-  <si>
-    <t>Yellow Mist</t>
-  </si>
-  <si>
-    <t>Red Berry</t>
-  </si>
-  <si>
-    <t>Very Red</t>
-  </si>
-  <si>
-    <t>Ducky Mauve</t>
-  </si>
-  <si>
-    <t>Purple Maze</t>
-  </si>
-  <si>
-    <t>Purple Twist</t>
-  </si>
-  <si>
-    <t>Purple Accent</t>
-  </si>
-  <si>
-    <t>Strawberry</t>
-  </si>
-  <si>
-    <t>Rhodamine</t>
-  </si>
-  <si>
-    <t>Ultra Blue</t>
-  </si>
-  <si>
-    <t>Tropic Blue</t>
-  </si>
-  <si>
-    <t>Empire Blue</t>
-  </si>
-  <si>
-    <t>Blue Suede</t>
-  </si>
-  <si>
-    <t>Blue Ink</t>
-  </si>
-  <si>
-    <t>M.D. Green</t>
-  </si>
-  <si>
-    <t>Oceanic Green</t>
-  </si>
-  <si>
-    <t>Green Bay</t>
-  </si>
-  <si>
-    <t>Peapod</t>
-  </si>
-  <si>
-    <t>Green Dust</t>
-  </si>
-  <si>
-    <t>Green Petal</t>
-  </si>
-  <si>
-    <t>Green Sail</t>
-  </si>
-  <si>
-    <t>Sunflower</t>
-  </si>
-  <si>
-    <t>Merit Gold</t>
-  </si>
-  <si>
-    <t>Nectar</t>
-  </si>
-  <si>
-    <t>Scholastic</t>
-  </si>
-  <si>
-    <t>Manila</t>
-  </si>
-  <si>
-    <t>Dark Texas Orange</t>
-  </si>
-  <si>
-    <t>Shimmering Gold</t>
-  </si>
-  <si>
-    <t>Auburn</t>
-  </si>
-  <si>
-    <t>Opaline</t>
-  </si>
-  <si>
-    <t>475C</t>
-  </si>
-  <si>
-    <t>Rattan</t>
-  </si>
-  <si>
-    <t>Seashell</t>
-  </si>
-  <si>
-    <t>Sand Dune</t>
-  </si>
-  <si>
-    <t>Lt. Cocoa</t>
-  </si>
-  <si>
-    <t>Almond</t>
-  </si>
-  <si>
-    <t>Hazel</t>
-  </si>
-  <si>
-    <t>Skylight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud </t>
-  </si>
-  <si>
-    <t>Saturn Gray</t>
-  </si>
-  <si>
-    <t>Storm Gray</t>
-  </si>
-  <si>
-    <t>Smokey</t>
-  </si>
-  <si>
-    <t>7547C</t>
-  </si>
-  <si>
-    <t>Cocoa Mulch</t>
-  </si>
-  <si>
-    <t>Wicker</t>
-  </si>
-  <si>
-    <t>J Turquoise</t>
-  </si>
-  <si>
-    <t>Cabernet</t>
-  </si>
-  <si>
-    <t>Warm Wine</t>
-  </si>
-  <si>
-    <t>Perfect Ruby</t>
-  </si>
-  <si>
-    <t>New Berry</t>
-  </si>
-  <si>
-    <t>Cherry Stone</t>
-  </si>
-  <si>
-    <t>Candy Apple Red</t>
-  </si>
-  <si>
-    <t>Dark Teal</t>
-  </si>
-  <si>
-    <t>Neon Green</t>
-  </si>
-  <si>
-    <t>Surf Blue</t>
-  </si>
-  <si>
-    <t>China Blue</t>
-  </si>
-  <si>
-    <t>PN Navy</t>
-  </si>
-  <si>
-    <t>Heron Blue</t>
-  </si>
-  <si>
-    <t>Dolphin Blue</t>
-  </si>
-  <si>
-    <t>Rockport Blue</t>
-  </si>
-  <si>
-    <t>CG1</t>
-  </si>
-  <si>
-    <t>Black Chrome</t>
-  </si>
-  <si>
-    <t>Foliage Green</t>
-  </si>
-  <si>
-    <t>Autumn Green</t>
-  </si>
-  <si>
-    <t>Blue Spruce</t>
-  </si>
-  <si>
-    <t>Newport</t>
-  </si>
-  <si>
-    <t>Ivy</t>
-  </si>
-  <si>
-    <t>Dark Army Green</t>
-  </si>
-  <si>
-    <t>Water Lilly</t>
-  </si>
-  <si>
-    <t>Pastel Green</t>
-  </si>
-  <si>
-    <t>Pollen Gold</t>
-  </si>
-  <si>
-    <t>Moonbeam</t>
-  </si>
-  <si>
-    <t>Black Eyed Susie</t>
-  </si>
-  <si>
-    <t>Golden Tan</t>
-  </si>
-  <si>
-    <t>Wonder Blue</t>
-  </si>
-  <si>
-    <t>Dress Green</t>
-  </si>
-  <si>
-    <t>Passion Rose</t>
-  </si>
-  <si>
-    <t>TH Gold</t>
-  </si>
-  <si>
-    <t>TH Green</t>
-  </si>
-  <si>
-    <t>Th Burgundy</t>
-  </si>
-  <si>
-    <t>Th Navy</t>
-  </si>
-  <si>
-    <t>Petal Pink</t>
-  </si>
-  <si>
-    <t>Bitteroot</t>
-  </si>
-  <si>
-    <t>D.H. Green</t>
-  </si>
-  <si>
-    <t>Azalea</t>
-  </si>
-  <si>
-    <t>Honeysuckle</t>
-  </si>
-  <si>
-    <t>Connor Green</t>
-  </si>
-  <si>
-    <t>Mountainview</t>
-  </si>
-  <si>
-    <t>Vassar Chic</t>
-  </si>
-  <si>
-    <t>Gray Flannel</t>
-  </si>
-  <si>
-    <t>Limerick</t>
-  </si>
-  <si>
-    <t>RA SSR 9</t>
-  </si>
-  <si>
-    <t>Lake blue</t>
-  </si>
-  <si>
-    <t>Blue Frost</t>
-  </si>
-  <si>
-    <t>Periwinkle</t>
-  </si>
-  <si>
-    <t>Pastel blue</t>
-  </si>
-  <si>
-    <t>Pacific Blue</t>
-  </si>
-  <si>
-    <t>Blue Horizon</t>
-  </si>
-  <si>
-    <t>Solar Blue</t>
-  </si>
-  <si>
-    <t>Indian Ocean</t>
-  </si>
-  <si>
-    <t>Bridgeport Blue</t>
-  </si>
-  <si>
-    <t>Country Blue</t>
-  </si>
-  <si>
-    <t>Bright Blue</t>
-  </si>
-  <si>
-    <t>Soldier Blue</t>
-  </si>
-  <si>
-    <t>Atlantis Blue</t>
-  </si>
-  <si>
-    <t>Caribbean Blue</t>
-  </si>
-  <si>
-    <t>Cadet Blue</t>
-  </si>
-  <si>
-    <t>Ozone</t>
-  </si>
-  <si>
-    <t>Salem Blue</t>
-  </si>
-  <si>
-    <t>Flag Blue</t>
-  </si>
-  <si>
-    <t>Pro Imperial</t>
-  </si>
-  <si>
-    <t>Pro Midnight</t>
-  </si>
-  <si>
-    <t>Pro Lusty Blue</t>
-  </si>
-  <si>
-    <t>Pro Twinkle</t>
-  </si>
-  <si>
-    <t>Pro Brilliance</t>
-  </si>
-  <si>
-    <t>Pro Dark Blue</t>
-  </si>
-  <si>
-    <t>Pro Saxon</t>
-  </si>
-  <si>
-    <t>Pro Navy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro Royal </t>
-  </si>
-  <si>
-    <t>Boo Boo Blue</t>
-  </si>
-  <si>
-    <t>Pro Peacock</t>
-  </si>
-  <si>
-    <t>Mocha Cream</t>
-  </si>
-  <si>
-    <t>Lt. Bronze</t>
-  </si>
-  <si>
-    <t>Dogwood</t>
-  </si>
-  <si>
-    <t>Mushroom</t>
-  </si>
-  <si>
-    <t>Perfect Tan</t>
-  </si>
-  <si>
-    <t>Earthen Tan</t>
-  </si>
-  <si>
-    <t>Aspen White</t>
-  </si>
-  <si>
-    <t>Dark Taupe</t>
-  </si>
-  <si>
-    <t>Egyptian Brown</t>
-  </si>
-  <si>
-    <t>Bone</t>
-  </si>
-  <si>
-    <t>Cottage Beige</t>
-  </si>
-  <si>
-    <t>Pro Brown</t>
-  </si>
-  <si>
-    <t>Pro Walnut</t>
-  </si>
-  <si>
-    <t>Peach</t>
-  </si>
-  <si>
-    <t>Steel</t>
-  </si>
-  <si>
-    <t>Stainless Steel</t>
-  </si>
-  <si>
-    <t>Traditional Gray</t>
-  </si>
-  <si>
-    <t>Gray Rod</t>
-  </si>
-  <si>
-    <t>Pewter</t>
-  </si>
-  <si>
-    <t>Silver Steel</t>
-  </si>
-  <si>
-    <t>Pro Night Sky</t>
-  </si>
-  <si>
-    <t>Pro Cool Gray</t>
-  </si>
-  <si>
-    <t>Pro Gray</t>
-  </si>
-  <si>
-    <t>Pro Pearl</t>
-  </si>
-  <si>
-    <t>Flite Green</t>
-  </si>
-  <si>
-    <t>Fleece Green</t>
-  </si>
-  <si>
-    <t>Bluestone</t>
-  </si>
-  <si>
-    <t>Aqua Pearl</t>
-  </si>
-  <si>
-    <t>Seafrost</t>
-  </si>
-  <si>
-    <t>Desert Cactus</t>
-  </si>
-  <si>
-    <t>Cypress</t>
-  </si>
-  <si>
-    <t>Crescent Moon</t>
-  </si>
-  <si>
-    <t>Pebblestone</t>
-  </si>
-  <si>
-    <t>Sun Shadow</t>
-  </si>
-  <si>
-    <t>Spring Garden</t>
-  </si>
-  <si>
-    <t>Harvest</t>
-  </si>
-  <si>
-    <t>Green Grass</t>
-  </si>
-  <si>
-    <t>Wintergreen</t>
-  </si>
-  <si>
-    <t>Sage</t>
-  </si>
-  <si>
-    <t>Jungle Green</t>
-  </si>
-  <si>
-    <t>Hedge</t>
-  </si>
-  <si>
-    <t>Pro Hunter</t>
-  </si>
-  <si>
-    <t>Pro Teal</t>
-  </si>
-  <si>
-    <t>Lizzy Green</t>
-  </si>
-  <si>
-    <t>Army Green</t>
-  </si>
-  <si>
-    <t>Pro Dark Green</t>
-  </si>
-  <si>
-    <t>Pro Green</t>
-  </si>
-  <si>
-    <t>Pro Erin</t>
-  </si>
-  <si>
-    <t>Pumpkin</t>
-  </si>
-  <si>
-    <t>Sun Orange</t>
-  </si>
-  <si>
-    <t>Tex Orange</t>
-  </si>
-  <si>
-    <t>Dark Tex Orange</t>
-  </si>
-  <si>
-    <t>Old DK Tex Orange</t>
-  </si>
-  <si>
-    <t>Bashful Pink</t>
-  </si>
-  <si>
-    <t>Persimmon</t>
-  </si>
-  <si>
-    <t>Rose</t>
-  </si>
-  <si>
-    <t>501C</t>
-  </si>
-  <si>
-    <t>Pink Mist</t>
-  </si>
-  <si>
-    <t>Emily Pink</t>
-  </si>
-  <si>
-    <t>Flesh</t>
-  </si>
-  <si>
-    <t>Floral Pink</t>
-  </si>
-  <si>
-    <t>Crimson</t>
-  </si>
-  <si>
-    <t>Primrose</t>
-  </si>
-  <si>
-    <t>Brushed Burgundy</t>
-  </si>
-  <si>
-    <t>Hot Peony</t>
-  </si>
-  <si>
-    <t>Rose Tint</t>
-  </si>
-  <si>
-    <t>Pro Cinnamon</t>
-  </si>
-  <si>
-    <t>Lavender</t>
-  </si>
-  <si>
-    <t>Mulberry</t>
-  </si>
-  <si>
-    <t>Cachet</t>
-  </si>
-  <si>
-    <t>Laurie Lilac</t>
-  </si>
-  <si>
-    <t>Raspberry</t>
-  </si>
-  <si>
-    <t>Violet Blue</t>
-  </si>
-  <si>
-    <t>Purple Shadow</t>
-  </si>
-  <si>
-    <t>Plum Wine</t>
-  </si>
-  <si>
-    <t>Mid Lilac</t>
-  </si>
-  <si>
-    <t>Port Wine</t>
-  </si>
-  <si>
-    <t>Pro Maroon</t>
-  </si>
-  <si>
-    <t>Pro Purple</t>
-  </si>
-  <si>
-    <t>Pro Brite Star</t>
-  </si>
-  <si>
-    <t>Pro Violet</t>
-  </si>
-  <si>
-    <t>Wildfire</t>
-  </si>
-  <si>
-    <t>Dark Maroon</t>
-  </si>
-  <si>
-    <t>Tuxedo Red</t>
-  </si>
-  <si>
-    <t>Red Jubilee</t>
-  </si>
-  <si>
-    <t>Antique Red</t>
-  </si>
-  <si>
-    <t>Rosewood</t>
-  </si>
-  <si>
-    <t>Pro Firebrand</t>
-  </si>
-  <si>
-    <t>Pro Red</t>
-  </si>
-  <si>
-    <t>Canary Yellow</t>
-  </si>
-  <si>
-    <t>Bright Yellow</t>
-  </si>
-  <si>
-    <t>Pale Yellow</t>
-  </si>
-  <si>
-    <t>Buttercup</t>
-  </si>
-  <si>
-    <t>Bullion</t>
-  </si>
-  <si>
-    <t>14 Kt. Gold</t>
-  </si>
-  <si>
-    <t>Marine Gold</t>
-  </si>
-  <si>
-    <t>24 Kt. Gold</t>
-  </si>
-  <si>
-    <t>Light Maize</t>
-  </si>
-  <si>
-    <t>Goldenlite</t>
-  </si>
-  <si>
-    <t>Pro Gold</t>
-  </si>
-  <si>
-    <t>Pro Maize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">         </t>
-  </si>
-  <si>
-    <t>Pro Beige</t>
   </si>
 </sst>
 </file>
@@ -1163,7 +1166,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4230,8 +4233,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFA00B30-AC3A-4274-A205-F06594091B29}">
-  <dimension ref="A1:I322"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O322"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" style="1" customWidth="1"/>
@@ -4239,14 +4242,14 @@
     <col min="4" max="4" width="19.7109375" style="288" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="17.7109375" style="1" customWidth="1"/>
-    <col min="7" max="9" width="8.85546875" style="1"/>
-    <col min="10" max="10" width="20.7109375" style="1" customWidth="1"/>
-    <col min="11" max="14" width="8.85546875" style="1"/>
-    <col min="15" max="15" width="50.7109375" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.85546875" style="1"/>
+    <col min="7" max="9" width="8.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" style="1" hidden="1" customWidth="1"/>
+    <col min="11" max="14" width="8.85546875" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="50.7109375" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.85546875" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="2" customFormat="1" ht="50.1" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4260,30 +4263,30 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:9" ht="50.1" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D2" s="5">
         <v>2300</v>
@@ -4302,15 +4305,15 @@
         <v>236</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="50.1" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>254</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D3" s="5">
         <v>2532</v>
@@ -4329,15 +4332,15 @@
         <v>229</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="50.1" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D4" s="5">
         <v>2283</v>
@@ -4356,15 +4359,15 @@
         <v>233</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="50.1" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D5" s="288">
         <v>2525</v>
@@ -4383,15 +4386,15 @@
         <v>232</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="50.1" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>243</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D6" s="288">
         <v>2382</v>
@@ -4410,15 +4413,15 @@
         <v>234</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="50.1" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>131</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D7" s="5">
         <v>2383</v>
@@ -4437,15 +4440,15 @@
         <v>237</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="50.1" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D8" s="5">
         <v>2239</v>
@@ -4464,15 +4467,15 @@
         <v>233</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="50.1" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>241</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D9" s="5">
         <v>2305</v>
@@ -4491,15 +4494,15 @@
         <v>222</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="50.1" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>249</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D10" s="5">
         <v>2524</v>
@@ -4518,15 +4521,15 @@
         <v>226</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="50.1" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>245</v>
+        <v>20</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D11" s="5">
         <v>2435</v>
@@ -4545,15 +4548,15 @@
         <v>228</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="50.1" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>158</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D12" s="288">
         <v>2434</v>
@@ -4572,15 +4575,15 @@
         <v>228</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="50.1" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>157</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D13" s="5">
         <v>2433</v>
@@ -4599,15 +4602,15 @@
         <v>231</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="50.1" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>248</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D14" s="288">
         <v>2522</v>
@@ -4626,15 +4629,15 @@
         <v>217</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="50.1" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D15" s="5">
         <v>2206</v>
@@ -4653,15 +4656,15 @@
         <v>226</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="50.1" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>240</v>
+        <v>25</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D16" s="5">
         <v>2304</v>
@@ -4680,15 +4683,15 @@
         <v>226</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="50.1" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>242</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D17" s="5">
         <v>2306</v>
@@ -4707,15 +4710,15 @@
         <v>222</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="50.1" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>247</v>
+        <v>27</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D18" s="5">
         <v>2518</v>
@@ -4734,15 +4737,15 @@
         <v>218</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="50.1" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>102</v>
+        <v>28</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D19" s="5">
         <v>2308</v>
@@ -4761,15 +4764,15 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="50.1" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>264</v>
+        <v>29</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D20" s="5">
         <v>2624</v>
@@ -4788,15 +4791,15 @@
         <v>195</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="50.1" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>261</v>
+        <v>30</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D21" s="5">
         <v>2617</v>
@@ -4815,15 +4818,15 @@
         <v>170</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="50.1" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D22" s="5">
         <v>2307</v>
@@ -4842,15 +4845,15 @@
         <v>205</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="50.1" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>253</v>
+        <v>32</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D23" s="288">
         <v>2530</v>
@@ -4869,15 +4872,15 @@
         <v>221</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="50.1" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D24" s="5">
         <v>2245</v>
@@ -4896,15 +4899,15 @@
         <v>220</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="50.1" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>250</v>
+        <v>34</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D25" s="5">
         <v>2526</v>
@@ -4923,15 +4926,15 @@
         <v>220</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="50.1" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>252</v>
+        <v>35</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D26" s="5">
         <v>2528</v>
@@ -4950,15 +4953,15 @@
         <v>220</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="50.1" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>260</v>
+        <v>36</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D27" s="5">
         <v>2614</v>
@@ -4977,15 +4980,15 @@
         <v>216</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="50.1" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>132</v>
+        <v>37</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D28" s="5">
         <v>2384</v>
@@ -5004,15 +5007,15 @@
         <v>216</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="50.1" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>202</v>
+        <v>38</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D29" s="5">
         <v>2519</v>
@@ -5031,15 +5034,15 @@
         <v>200</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="50.1" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>136</v>
+        <v>39</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D30" s="5">
         <v>2389</v>
@@ -5058,15 +5061,15 @@
         <v>200</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="50.1" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>244</v>
+        <v>40</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D31" s="5">
         <v>2388</v>
@@ -5085,15 +5088,15 @@
         <v>185</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="50.1" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>267</v>
+        <v>41</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D32" s="5">
         <v>2730</v>
@@ -5112,15 +5115,15 @@
         <v>185</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" ht="50.1" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>246</v>
+        <v>42</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D33" s="5">
         <v>2442</v>
@@ -5139,15 +5142,15 @@
         <v>208</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="50.1" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>255</v>
+        <v>43</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D34" s="5">
         <v>2533</v>
@@ -5166,15 +5169,15 @@
         <v>185</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="50.1" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>222</v>
+        <v>44</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D35" s="5">
         <v>2577</v>
@@ -5193,15 +5196,15 @@
         <v>158</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" ht="50.1" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D36" s="5">
         <v>2220</v>
@@ -5220,15 +5223,15 @@
         <v>185</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" ht="50.1" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D37" s="5">
         <v>2280</v>
@@ -5247,15 +5250,15 @@
         <v>185</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" ht="50.1" customHeight="1">
       <c r="A38" s="1" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D38" s="5">
         <v>2275</v>
@@ -5274,15 +5277,15 @@
         <v>147</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" ht="50.1" customHeight="1">
       <c r="A39" s="1" t="s">
-        <v>268</v>
+        <v>48</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D39" s="5">
         <v>2740</v>
@@ -5301,15 +5304,15 @@
         <v>165</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" ht="50.1" customHeight="1">
       <c r="A40" s="1" t="s">
-        <v>258</v>
+        <v>49</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D40" s="5">
         <v>2612</v>
@@ -5328,15 +5331,15 @@
         <v>145</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" ht="50.1" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>203</v>
+        <v>50</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D41" s="5">
         <v>2523</v>
@@ -5355,15 +5358,15 @@
         <v>147</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" ht="50.1" customHeight="1">
       <c r="A42" s="1" t="s">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D42" s="5">
         <v>2302</v>
@@ -5382,15 +5385,15 @@
         <v>143</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" ht="50.1" customHeight="1">
       <c r="A43" s="1" t="s">
-        <v>251</v>
+        <v>52</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D43" s="5">
         <v>2527</v>
@@ -5409,15 +5412,15 @@
         <v>150</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" ht="50.1" customHeight="1">
       <c r="A44" s="1" t="s">
-        <v>262</v>
+        <v>53</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D44" s="5">
         <v>2619</v>
@@ -5436,15 +5439,15 @@
         <v>165</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" ht="50.1" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>160</v>
+        <v>54</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D45" s="5">
         <v>2438</v>
@@ -5463,15 +5466,15 @@
         <v>159</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" ht="50.1" customHeight="1">
       <c r="A46" s="1" t="s">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D46" s="5">
         <v>2385</v>
@@ -5490,15 +5493,15 @@
         <v>147</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" ht="50.1" customHeight="1">
       <c r="A47" s="1" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D47" s="5">
         <v>2437</v>
@@ -5517,15 +5520,15 @@
         <v>141</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" ht="50.1" customHeight="1">
       <c r="A48" s="1" t="s">
-        <v>266</v>
+        <v>57</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D48" s="5">
         <v>2627</v>
@@ -5544,15 +5547,15 @@
         <v>133</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" ht="50.1" customHeight="1">
       <c r="A49" s="1" t="s">
-        <v>259</v>
+        <v>58</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D49" s="5">
         <v>2613</v>
@@ -5571,15 +5574,15 @@
         <v>102</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" ht="50.1" customHeight="1">
       <c r="A50" s="1" t="s">
-        <v>125</v>
+        <v>59</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D50" s="5">
         <v>2341</v>
@@ -5598,15 +5601,15 @@
         <v>93</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" ht="50.1" customHeight="1">
       <c r="A51" s="1" t="s">
-        <v>134</v>
+        <v>60</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D51" s="5">
         <v>2386</v>
@@ -5625,15 +5628,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" ht="50.1" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>161</v>
+        <v>61</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D52" s="5">
         <v>2440</v>
@@ -5652,15 +5655,15 @@
         <v>106</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" ht="50.1" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>263</v>
+        <v>62</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D53" s="5">
         <v>2620</v>
@@ -5679,15 +5682,15 @@
         <v>90</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" ht="50.1" customHeight="1">
       <c r="A54" s="1" t="s">
-        <v>256</v>
+        <v>63</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D54" s="5">
         <v>2534</v>
@@ -5706,15 +5709,15 @@
         <v>99</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" ht="50.1" customHeight="1">
       <c r="A55" s="1" t="s">
-        <v>265</v>
+        <v>64</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D55" s="288">
         <v>2625</v>
@@ -5733,15 +5736,15 @@
         <v>104</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" ht="50.1" customHeight="1">
       <c r="A56" s="1" t="s">
-        <v>257</v>
+        <v>65</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D56" s="5">
         <v>2603</v>
@@ -5760,15 +5763,15 @@
         <v>74</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" ht="50.1" customHeight="1">
       <c r="A57" s="1" t="s">
-        <v>228</v>
+        <v>66</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D57" s="5">
         <v>2609</v>
@@ -5787,22 +5790,22 @@
         <v>72</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" ht="50.1" customHeight="1">
       <c r="A58" s="1" t="s">
-        <v>189</v>
+        <v>67</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D58" s="5">
         <v>2487</v>
       </c>
       <c r="E58" s="251"/>
       <c r="F58" s="1" t="s">
-        <v>190</v>
+        <v>68</v>
       </c>
       <c r="G58" s="1">
         <v>21</v>
@@ -5814,15 +5817,15 @@
         <v>39</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" ht="50.1" customHeight="1">
       <c r="A59" s="1" t="s">
-        <v>126</v>
+        <v>69</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D59" s="5">
         <v>2342</v>
@@ -5841,15 +5844,15 @@
         <v>202</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" ht="50.1" customHeight="1">
       <c r="A60" s="1" t="s">
-        <v>275</v>
+        <v>71</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D60" s="288">
         <v>2574</v>
@@ -5868,15 +5871,15 @@
         <v>202</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" ht="50.1" customHeight="1">
       <c r="A61" s="1" t="s">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D61" s="5">
         <v>2335</v>
@@ -5895,15 +5898,15 @@
         <v>176</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" ht="50.1" customHeight="1">
       <c r="A62" s="1" t="s">
-        <v>278</v>
+        <v>73</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D62" s="288">
         <v>2582</v>
@@ -5922,15 +5925,15 @@
         <v>176</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" ht="50.1" customHeight="1">
       <c r="A63" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D63" s="5">
         <v>2232</v>
@@ -5949,15 +5952,15 @@
         <v>179</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" ht="50.1" customHeight="1">
       <c r="A64" s="1" t="s">
-        <v>279</v>
+        <v>75</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D64" s="5">
         <v>2593</v>
@@ -5976,15 +5979,15 @@
         <v>182</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" ht="50.1" customHeight="1">
       <c r="A65" s="1" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D65" s="5">
         <v>2203</v>
@@ -6003,15 +6006,15 @@
         <v>139</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" ht="50.1" customHeight="1">
       <c r="A66" s="1" t="s">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D66" s="5">
         <v>2476</v>
@@ -6030,15 +6033,15 @@
         <v>133</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" ht="50.1" customHeight="1">
       <c r="A67" s="1" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D67" s="5">
         <v>2336</v>
@@ -6057,15 +6060,15 @@
         <v>132</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" ht="50.1" customHeight="1">
       <c r="A68" s="1" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D68" s="5">
         <v>2571</v>
@@ -6084,15 +6087,15 @@
         <v>153</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" ht="50.1" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D69" s="5">
         <v>2273</v>
@@ -6111,15 +6114,15 @@
         <v>115</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" ht="50.1" customHeight="1">
       <c r="A70" s="1" t="s">
-        <v>371</v>
+        <v>81</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D70" s="288">
         <v>2630</v>
@@ -6138,15 +6141,15 @@
         <v>92</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" ht="50.1" customHeight="1">
       <c r="A71" s="1" t="s">
-        <v>269</v>
+        <v>83</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D71" s="5">
         <v>2475</v>
@@ -6165,15 +6168,15 @@
         <v>115</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" ht="50.1" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D72" s="288">
         <v>2338</v>
@@ -6192,15 +6195,15 @@
         <v>115</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" ht="50.1" customHeight="1">
       <c r="A73" s="1" t="s">
-        <v>273</v>
+        <v>85</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D73" s="5">
         <v>2568</v>
@@ -6219,15 +6222,15 @@
         <v>126</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" ht="50.1" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>141</v>
+        <v>86</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D74" s="5">
         <v>2401</v>
@@ -6246,15 +6249,15 @@
         <v>106</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" ht="50.1" customHeight="1">
       <c r="A75" s="1" t="s">
-        <v>140</v>
+        <v>87</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D75" s="5">
         <v>2400</v>
@@ -6273,15 +6276,15 @@
         <v>78</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" ht="50.1" customHeight="1">
       <c r="A76" s="1" t="s">
-        <v>192</v>
+        <v>88</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D76" s="5">
         <v>2489</v>
@@ -6300,15 +6303,15 @@
         <v>85</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" ht="50.1" customHeight="1">
       <c r="A77" s="1" t="s">
-        <v>270</v>
+        <v>89</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D77" s="5">
         <v>2493</v>
@@ -6327,15 +6330,15 @@
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" ht="50.1" customHeight="1">
       <c r="A78" s="1" t="s">
-        <v>179</v>
+        <v>90</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D78" s="5">
         <v>2474</v>
@@ -6354,15 +6357,15 @@
         <v>113</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" ht="50.1" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>183</v>
+        <v>91</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D79" s="288">
         <v>2479</v>
@@ -6381,15 +6384,15 @@
         <v>31</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" ht="50.1" customHeight="1">
       <c r="A80" s="1" t="s">
-        <v>272</v>
+        <v>92</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D80" s="288">
         <v>2567</v>
@@ -6408,15 +6411,15 @@
         <v>115</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" ht="50.1" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>29</v>
+        <v>93</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D81" s="5">
         <v>2295</v>
@@ -6435,15 +6438,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" ht="50.1" customHeight="1">
       <c r="A82" s="1" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D82" s="5">
         <v>2231</v>
@@ -6462,15 +6465,15 @@
         <v>24</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" ht="50.1" customHeight="1">
       <c r="A83" s="1" t="s">
-        <v>280</v>
+        <v>95</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D83" s="5">
         <v>2610</v>
@@ -6489,15 +6492,15 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" ht="50.1" customHeight="1">
       <c r="A84" s="1" t="s">
-        <v>191</v>
+        <v>96</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D84" s="5">
         <v>2488</v>
@@ -6516,15 +6519,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" ht="50.1" customHeight="1">
       <c r="A85" s="1" t="s">
-        <v>184</v>
+        <v>97</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D85" s="5">
         <v>2481</v>
@@ -6543,15 +6546,15 @@
         <v>37</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" ht="50.1" customHeight="1">
       <c r="A86" s="1" t="s">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D86" s="5">
         <v>2205</v>
@@ -6570,15 +6573,15 @@
         <v>48</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" ht="50.1" customHeight="1">
       <c r="A87" s="1" t="s">
-        <v>181</v>
+        <v>99</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D87" s="5">
         <v>2477</v>
@@ -6597,15 +6600,15 @@
         <v>61</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" ht="50.1" customHeight="1">
       <c r="A88" s="1" t="s">
-        <v>274</v>
+        <v>100</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D88" s="5">
         <v>2569</v>
@@ -6624,15 +6627,15 @@
         <v>68</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" ht="50.1" customHeight="1">
       <c r="A89" s="1" t="s">
-        <v>182</v>
+        <v>101</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D89" s="5">
         <v>2478</v>
@@ -6651,15 +6654,15 @@
         <v>57</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" ht="50.1" customHeight="1">
       <c r="A90" s="1" t="s">
-        <v>281</v>
+        <v>102</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D90" s="5">
         <v>2629</v>
@@ -6678,15 +6681,15 @@
         <v>52</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" ht="50.1" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D91" s="5">
         <v>2227</v>
@@ -6705,15 +6708,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" ht="50.1" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>142</v>
+        <v>104</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D92" s="5">
         <v>2402</v>
@@ -6732,15 +6735,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" ht="50.1" customHeight="1">
       <c r="A93" s="1" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D93" s="288">
         <v>2290</v>
@@ -6759,15 +6762,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" ht="50.1" customHeight="1">
       <c r="A94" s="1" t="s">
-        <v>271</v>
+        <v>106</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D94" s="5">
         <v>2563</v>
@@ -6786,15 +6789,15 @@
         <v>70</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" ht="50.1" customHeight="1">
       <c r="A95" s="1" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D95" s="5">
         <v>2339</v>
@@ -6813,15 +6816,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" ht="50.1" customHeight="1">
       <c r="A96" s="1" t="s">
-        <v>276</v>
+        <v>108</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D96" s="5">
         <v>2575</v>
@@ -6840,15 +6843,15 @@
         <v>54</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" ht="41.25" customHeight="1">
       <c r="A97" s="1" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D97" s="5">
         <v>2372</v>
@@ -6867,15 +6870,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" ht="50.1" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D98" s="5">
         <v>2337</v>
@@ -6894,15 +6897,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" ht="42" customHeight="1">
       <c r="A99" s="1" t="s">
-        <v>277</v>
+        <v>111</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D99" s="5">
         <v>2576</v>
@@ -6921,15 +6924,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" ht="50.1" customHeight="1">
       <c r="A100" s="1" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D100" s="5">
         <v>2274</v>
@@ -6948,15 +6951,15 @@
         <v>224</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" ht="50.1" customHeight="1">
       <c r="A101" s="1" t="s">
-        <v>288</v>
+        <v>114</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D101" s="5">
         <v>2592</v>
@@ -6975,22 +6978,22 @@
         <v>222</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" ht="50.1" customHeight="1">
       <c r="A102" s="1" t="s">
-        <v>283</v>
+        <v>115</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D102" s="5">
         <v>2537</v>
       </c>
       <c r="E102" s="138"/>
       <c r="F102" s="1" t="s">
-        <v>208</v>
+        <v>116</v>
       </c>
       <c r="G102" s="1">
         <v>218</v>
@@ -7002,22 +7005,22 @@
         <v>215</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" ht="50.1" customHeight="1">
       <c r="A103" s="1" t="s">
-        <v>28</v>
+        <v>117</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D103" s="5">
         <v>2539</v>
       </c>
       <c r="E103" s="138"/>
       <c r="F103" s="1" t="s">
-        <v>208</v>
+        <v>116</v>
       </c>
       <c r="G103" s="1">
         <v>218</v>
@@ -7029,15 +7032,15 @@
         <v>215</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" ht="50.1" customHeight="1">
       <c r="A104" s="1" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D104" s="5">
         <v>2403</v>
@@ -7056,22 +7059,22 @@
         <v>211</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" ht="50.1" customHeight="1">
       <c r="A105" s="1" t="s">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D105" s="5">
         <v>2207</v>
       </c>
       <c r="E105" s="199"/>
       <c r="F105" s="1">
-        <v>5424</v>
+        <v>5245</v>
       </c>
       <c r="G105" s="1">
         <v>221</v>
@@ -7083,15 +7086,15 @@
         <v>210</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" ht="50.1" customHeight="1">
       <c r="A106" s="1" t="s">
-        <v>185</v>
+        <v>120</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D106" s="288">
         <v>2482</v>
@@ -7110,15 +7113,15 @@
         <v>209</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" ht="50.1" customHeight="1">
       <c r="A107" s="1" t="s">
-        <v>187</v>
+        <v>121</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D107" s="5">
         <v>2485</v>
@@ -7137,15 +7140,15 @@
         <v>209</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" ht="50.1" customHeight="1">
       <c r="A108" s="1" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D108" s="5">
         <v>2405</v>
@@ -7164,15 +7167,15 @@
         <v>214</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" ht="41.25" customHeight="1">
       <c r="A109" s="1" t="s">
-        <v>285</v>
+        <v>123</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D109" s="5">
         <v>2540</v>
@@ -7191,15 +7194,15 @@
         <v>215</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" ht="50.1" customHeight="1">
       <c r="A110" s="1" t="s">
-        <v>284</v>
+        <v>124</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D110" s="5">
         <v>2538</v>
@@ -7218,15 +7221,15 @@
         <v>198</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" ht="50.1" customHeight="1">
       <c r="A111" s="1" t="s">
-        <v>188</v>
+        <v>125</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D111" s="5">
         <v>2486</v>
@@ -7245,15 +7248,15 @@
         <v>195</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" ht="50.1" customHeight="1">
       <c r="A112" s="1" t="s">
-        <v>290</v>
+        <v>126</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D112" s="5">
         <v>2733</v>
@@ -7272,15 +7275,15 @@
         <v>182</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" ht="50.1" customHeight="1">
       <c r="A113" s="1" t="s">
-        <v>292</v>
+        <v>127</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D113" s="5">
         <v>2741</v>
@@ -7299,15 +7302,15 @@
         <v>186</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" ht="50.1" customHeight="1">
       <c r="A114" s="1" t="s">
-        <v>186</v>
+        <v>128</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D114" s="5">
         <v>2483</v>
@@ -7326,15 +7329,15 @@
         <v>161</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" ht="50.1" customHeight="1">
       <c r="A115" s="1" t="s">
-        <v>289</v>
+        <v>129</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D115" s="5">
         <v>2618</v>
@@ -7353,15 +7356,15 @@
         <v>161</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" ht="50.1" customHeight="1">
       <c r="A116" s="1" t="s">
-        <v>286</v>
+        <v>130</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D116" s="5">
         <v>2572</v>
@@ -7380,15 +7383,15 @@
         <v>130</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" ht="50.1" customHeight="1">
       <c r="A117" s="1" t="s">
-        <v>291</v>
+        <v>131</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D117" s="5">
         <v>2739</v>
@@ -7407,15 +7410,15 @@
         <v>130</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" ht="50.1" customHeight="1">
       <c r="A118" s="1" t="s">
-        <v>287</v>
+        <v>132</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D118" s="5">
         <v>2573</v>
@@ -7434,15 +7437,15 @@
         <v>122</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" ht="50.1" customHeight="1">
       <c r="A119" s="1" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D119" s="5">
         <v>2217</v>
@@ -7461,22 +7464,22 @@
         <v>106</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" ht="50.1" customHeight="1">
       <c r="A120" s="1" t="s">
-        <v>209</v>
+        <v>134</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D120" s="5">
         <v>2541</v>
       </c>
       <c r="E120" s="258"/>
       <c r="F120" s="1" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="G120" s="1">
         <v>60</v>
@@ -7488,15 +7491,15 @@
         <v>52</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" ht="50.1" customHeight="1">
       <c r="A121" s="1" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D121" s="288">
         <v>2316</v>
@@ -7515,15 +7518,15 @@
         <v>176</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" ht="50.1" customHeight="1">
       <c r="A122" s="1" t="s">
-        <v>217</v>
+        <v>138</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D122" s="5">
         <v>2555</v>
@@ -7542,15 +7545,15 @@
         <v>186</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" ht="50.1" customHeight="1">
       <c r="A123" s="1" t="s">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D123" s="5">
         <v>2238</v>
@@ -7569,15 +7572,15 @@
         <v>179</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" ht="50.1" customHeight="1">
       <c r="A124" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D124" s="5">
         <v>2393</v>
@@ -7596,15 +7599,15 @@
         <v>226</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" ht="50.1" customHeight="1">
       <c r="A125" s="1" t="s">
-        <v>297</v>
+        <v>141</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D125" s="5">
         <v>2517</v>
@@ -7623,15 +7626,15 @@
         <v>216</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" ht="50.1" customHeight="1">
       <c r="A126" s="1" t="s">
-        <v>301</v>
+        <v>142</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D126" s="5">
         <v>2547</v>
@@ -7650,15 +7653,15 @@
         <v>134</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" ht="50.1" customHeight="1">
       <c r="A127" s="1" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D127" s="5">
         <v>2319</v>
@@ -7677,15 +7680,15 @@
         <v>142</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" ht="50.1" customHeight="1">
       <c r="A128" s="1" t="s">
-        <v>293</v>
+        <v>144</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D128" s="5">
         <v>2282</v>
@@ -7704,15 +7707,15 @@
         <v>148</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" ht="50.1" customHeight="1">
       <c r="A129" s="1" t="s">
-        <v>63</v>
+        <v>145</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D129" s="5">
         <v>2241</v>
@@ -7731,15 +7734,15 @@
         <v>176</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" ht="50.1" customHeight="1">
       <c r="A130" s="1" t="s">
-        <v>42</v>
+        <v>146</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D130" s="5">
         <v>2211</v>
@@ -7758,15 +7761,15 @@
         <v>106</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" ht="50.1" customHeight="1">
       <c r="A131" s="1" t="s">
-        <v>302</v>
+        <v>147</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D131" s="5">
         <v>2548</v>
@@ -7785,15 +7788,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" ht="50.1" customHeight="1">
       <c r="A132" s="1" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D132" s="5">
         <v>2456</v>
@@ -7812,15 +7815,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" ht="50.1" customHeight="1">
       <c r="A133" s="1" t="s">
-        <v>296</v>
+        <v>149</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D133" s="5">
         <v>2516</v>
@@ -7839,15 +7842,15 @@
         <v>197</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" ht="50.1" customHeight="1">
       <c r="A134" s="1" t="s">
-        <v>303</v>
+        <v>150</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D134" s="5">
         <v>2551</v>
@@ -7866,15 +7869,15 @@
         <v>150</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" ht="50.1" customHeight="1">
       <c r="A135" s="1" t="s">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D135" s="5">
         <v>2320</v>
@@ -7893,15 +7896,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" ht="50.1" customHeight="1">
       <c r="A136" s="1" t="s">
-        <v>32</v>
+        <v>152</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D136" s="5">
         <v>2204</v>
@@ -7920,15 +7923,15 @@
         <v>179</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" ht="50.1" customHeight="1">
       <c r="A137" s="1" t="s">
-        <v>306</v>
+        <v>153</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D137" s="5">
         <v>2594</v>
@@ -7947,15 +7950,15 @@
         <v>135</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" ht="50.1" customHeight="1">
       <c r="A138" s="1" t="s">
-        <v>85</v>
+        <v>154</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D138" s="5">
         <v>2278</v>
@@ -7974,15 +7977,15 @@
         <v>145</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" ht="50.1" customHeight="1">
       <c r="A139" s="1" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D139" s="5">
         <v>2457</v>
@@ -8001,15 +8004,15 @@
         <v>70</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" ht="50.1" customHeight="1">
       <c r="A140" s="1" t="s">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D140" s="5">
         <v>2214</v>
@@ -8028,15 +8031,15 @@
         <v>61</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" ht="50.1" customHeight="1">
       <c r="A141" s="1" t="s">
-        <v>86</v>
+        <v>157</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D141" s="5">
         <v>2279</v>
@@ -8055,15 +8058,15 @@
         <v>70</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" ht="50.1" customHeight="1">
       <c r="A142" s="1" t="s">
-        <v>193</v>
+        <v>158</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D142" s="5">
         <v>2492</v>
@@ -8082,21 +8085,21 @@
         <v>143</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" ht="50.1" customHeight="1">
       <c r="A143" s="1" t="s">
-        <v>295</v>
+        <v>159</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D143" s="5">
         <v>2515</v>
       </c>
       <c r="E143" s="141" t="s">
-        <v>370</v>
+        <v>160</v>
       </c>
       <c r="F143" s="1">
         <v>3285</v>
@@ -8111,15 +8114,15 @@
         <v>129</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" ht="50.1" customHeight="1">
       <c r="A144" s="1" t="s">
-        <v>51</v>
+        <v>161</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D144" s="5">
         <v>2226</v>
@@ -8138,15 +8141,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" ht="50.1" customHeight="1">
       <c r="A145" s="1" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D145" s="288">
         <v>2230</v>
@@ -8165,15 +8168,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" ht="50.1" customHeight="1">
       <c r="A146" s="1" t="s">
-        <v>300</v>
+        <v>163</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D146" s="5">
         <v>2546</v>
@@ -8192,15 +8195,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" ht="50.1" customHeight="1">
       <c r="A147" s="1" t="s">
-        <v>308</v>
+        <v>164</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D147" s="5">
         <v>2597</v>
@@ -8219,15 +8222,15 @@
         <v>120</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" ht="50.1" customHeight="1">
       <c r="A148" s="1" t="s">
-        <v>213</v>
+        <v>165</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D148" s="5">
         <v>2550</v>
@@ -8246,15 +8249,15 @@
         <v>115</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" ht="50.1" customHeight="1">
       <c r="A149" s="1" t="s">
-        <v>304</v>
+        <v>166</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D149" s="5">
         <v>2578</v>
@@ -8273,15 +8276,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" ht="50.1" customHeight="1">
       <c r="A150" s="1" t="s">
-        <v>210</v>
+        <v>167</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D150" s="5">
         <v>2542</v>
@@ -8300,15 +8303,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" ht="50.1" customHeight="1">
       <c r="A151" s="1" t="s">
-        <v>316</v>
+        <v>168</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D151" s="5">
         <v>2738</v>
@@ -8327,15 +8330,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" ht="50.1" customHeight="1">
       <c r="A152" s="1" t="s">
-        <v>305</v>
+        <v>169</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D152" s="5">
         <v>2580</v>
@@ -8354,15 +8357,15 @@
         <v>55</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" ht="50.1" customHeight="1">
       <c r="A153" s="1" t="s">
-        <v>22</v>
+        <v>170</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D153" s="5">
         <v>2209</v>
@@ -8381,15 +8384,15 @@
         <v>59</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" ht="50.1" customHeight="1">
       <c r="A154" s="1" t="s">
-        <v>211</v>
+        <v>171</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D154" s="5">
         <v>2543</v>
@@ -8408,15 +8411,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" ht="50.1" customHeight="1">
       <c r="A155" s="1" t="s">
-        <v>104</v>
+        <v>172</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D155" s="5">
         <v>2312</v>
@@ -8435,15 +8438,15 @@
         <v>122</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" ht="50.1" customHeight="1">
       <c r="A156" s="1" t="s">
-        <v>38</v>
+        <v>173</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D156" s="5">
         <v>2202</v>
@@ -8462,15 +8465,15 @@
         <v>112</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" ht="50.1" customHeight="1">
       <c r="A157" s="1" t="s">
-        <v>216</v>
+        <v>174</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D157" s="5">
         <v>2554</v>
@@ -8489,15 +8492,15 @@
         <v>112</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" ht="50.1" customHeight="1">
       <c r="A158" s="1" t="s">
-        <v>311</v>
+        <v>175</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D158" s="5">
         <v>2621</v>
@@ -8516,15 +8519,15 @@
         <v>126</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" ht="50.1" customHeight="1">
       <c r="A159" s="1" t="s">
-        <v>103</v>
+        <v>176</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D159" s="5">
         <v>2309</v>
@@ -8543,15 +8546,15 @@
         <v>150</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" ht="50.1" customHeight="1">
       <c r="A160" s="1" t="s">
-        <v>48</v>
+        <v>177</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D160" s="5">
         <v>2221</v>
@@ -8570,15 +8573,15 @@
         <v>96</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" ht="50.1" customHeight="1">
       <c r="A161" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="C161" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D161" s="5">
         <v>2391</v>
@@ -8597,15 +8600,15 @@
         <v>101</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" ht="50.1" customHeight="1">
       <c r="A162" s="1" t="s">
-        <v>62</v>
+        <v>179</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D162" s="5">
         <v>2240</v>
@@ -8624,15 +8627,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" ht="50.1" customHeight="1">
       <c r="A163" s="1" t="s">
-        <v>299</v>
+        <v>180</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D163" s="5">
         <v>2545</v>
@@ -8651,15 +8654,15 @@
         <v>24</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" ht="50.1" customHeight="1">
       <c r="A164" s="1" t="s">
-        <v>53</v>
+        <v>181</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D164" s="5">
         <v>2229</v>
@@ -8678,15 +8681,15 @@
         <v>23</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" ht="50.1" customHeight="1">
       <c r="A165" s="1" t="s">
-        <v>298</v>
+        <v>182</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D165" s="5">
         <v>2544</v>
@@ -8705,15 +8708,15 @@
         <v>29</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" ht="49.5" customHeight="1">
       <c r="A166" s="1" t="s">
-        <v>107</v>
+        <v>183</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D166" s="5">
         <v>2317</v>
@@ -8732,15 +8735,15 @@
         <v>24</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" ht="50.1" customHeight="1">
       <c r="A167" s="1" t="s">
-        <v>307</v>
+        <v>184</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D167" s="5">
         <v>2595</v>
@@ -8759,15 +8762,15 @@
         <v>58</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" ht="50.1" customHeight="1">
       <c r="A168" s="1" t="s">
-        <v>89</v>
+        <v>185</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D168" s="5">
         <v>2284</v>
@@ -8786,15 +8789,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" ht="50.1" customHeight="1">
       <c r="A169" s="1" t="s">
-        <v>310</v>
+        <v>186</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D169" s="5">
         <v>2615</v>
@@ -8813,15 +8816,15 @@
         <v>93</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" ht="50.1" customHeight="1">
       <c r="A170" s="1" t="s">
-        <v>294</v>
+        <v>187</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D170" s="5">
         <v>2454</v>
@@ -8840,15 +8843,15 @@
         <v>82</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" ht="50.1" customHeight="1">
       <c r="A171" s="1" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D171" s="5">
         <v>2455</v>
@@ -8867,15 +8870,15 @@
         <v>71</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" ht="50.1" customHeight="1">
       <c r="A172" s="1" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D172" s="5">
         <v>2607</v>
@@ -8894,15 +8897,15 @@
         <v>79</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" ht="50.1" customHeight="1">
       <c r="A173" s="1" t="s">
-        <v>105</v>
+        <v>190</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D173" s="5">
         <v>2315</v>
@@ -8921,15 +8924,15 @@
         <v>64</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" ht="50.1" customHeight="1">
       <c r="A174" s="1" t="s">
-        <v>111</v>
+        <v>191</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D174" s="5">
         <v>2323</v>
@@ -8948,15 +8951,15 @@
         <v>55</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" ht="50.1" customHeight="1">
       <c r="A175" s="1" t="s">
-        <v>138</v>
+        <v>192</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D175" s="288">
         <v>2392</v>
@@ -8975,15 +8978,15 @@
         <v>76</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" ht="50.1" customHeight="1">
       <c r="A176" s="1" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D176" s="5">
         <v>2549</v>
@@ -9002,15 +9005,15 @@
         <v>79</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" ht="50.1" customHeight="1">
       <c r="A177" s="1" t="s">
-        <v>223</v>
+        <v>194</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D177" s="5">
         <v>2584</v>
@@ -9029,15 +9032,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" ht="50.1" customHeight="1">
       <c r="A178" s="1" t="s">
-        <v>315</v>
+        <v>195</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D178" s="288">
         <v>2735</v>
@@ -9056,15 +9059,15 @@
         <v>75</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" ht="50.1" customHeight="1">
       <c r="A179" s="1" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D179" s="5">
         <v>2552</v>
@@ -9083,15 +9086,15 @@
         <v>65</v>
       </c>
     </row>
-    <row r="180" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" ht="50.1" customHeight="1">
       <c r="A180" s="1" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D180" s="5">
         <v>2553</v>
@@ -9110,15 +9113,15 @@
         <v>65</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" ht="50.1" customHeight="1">
       <c r="A181" s="1" t="s">
-        <v>309</v>
+        <v>198</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D181" s="288">
         <v>2601</v>
@@ -9137,15 +9140,15 @@
         <v>37</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" ht="50.1" customHeight="1">
       <c r="A182" s="1" t="s">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D182" s="5">
         <v>2458</v>
@@ -9164,15 +9167,15 @@
         <v>51</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" ht="50.1" customHeight="1">
       <c r="A183" s="1" t="s">
-        <v>312</v>
+        <v>200</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D183" s="288">
         <v>2631</v>
@@ -9191,15 +9194,15 @@
         <v>51</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" ht="50.1" customHeight="1">
       <c r="A184" s="1" t="s">
-        <v>314</v>
+        <v>201</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D184" s="5">
         <v>2734</v>
@@ -9218,15 +9221,15 @@
         <v>55</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" ht="50.1" customHeight="1">
       <c r="A185" s="1" t="s">
-        <v>168</v>
+        <v>202</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D185" s="288">
         <v>2459</v>
@@ -9245,15 +9248,15 @@
         <v>52</v>
       </c>
     </row>
-    <row r="186" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" ht="50.1" customHeight="1">
       <c r="A186" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D186" s="5">
         <v>2444</v>
@@ -9272,15 +9275,15 @@
         <v>81</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" ht="50.1" customHeight="1">
       <c r="A187" s="1" t="s">
-        <v>231</v>
+        <v>204</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D187" s="288">
         <v>2411</v>
@@ -9299,15 +9302,15 @@
         <v>43</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" ht="50.1" customHeight="1">
       <c r="A188" s="1" t="s">
-        <v>313</v>
+        <v>205</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D188" s="288">
         <v>2728</v>
@@ -9326,15 +9329,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="189" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" ht="50.1" customHeight="1">
       <c r="A189" s="1" t="s">
-        <v>317</v>
+        <v>206</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>10</v>
+        <v>207</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D189" s="5">
         <v>2328</v>
@@ -9353,15 +9356,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" ht="50.1" customHeight="1">
       <c r="A190" s="1" t="s">
-        <v>115</v>
+        <v>208</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>10</v>
+        <v>207</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D190" s="5">
         <v>2330</v>
@@ -9380,15 +9383,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="191" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" ht="50.1" customHeight="1">
       <c r="A191" s="1" t="s">
-        <v>320</v>
+        <v>209</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>10</v>
+        <v>207</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D191" s="288">
         <v>2469</v>
@@ -9407,15 +9410,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="192" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" ht="50.1" customHeight="1">
       <c r="A192" s="1" t="s">
-        <v>59</v>
+        <v>210</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>10</v>
+        <v>207</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D192" s="5">
         <v>2236</v>
@@ -9434,15 +9437,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" ht="50.1" customHeight="1">
       <c r="A193" s="1" t="s">
-        <v>319</v>
+        <v>211</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>10</v>
+        <v>207</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D193" s="288">
         <v>2468</v>
@@ -9461,15 +9464,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" ht="50.1" customHeight="1">
       <c r="A194" s="1" t="s">
-        <v>318</v>
+        <v>212</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>10</v>
+        <v>207</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D194" s="5">
         <v>2397</v>
@@ -9488,15 +9491,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" ht="50.1" customHeight="1">
       <c r="A195" s="1" t="s">
-        <v>94</v>
+        <v>213</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>10</v>
+        <v>207</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D195" s="5">
         <v>2289</v>
@@ -9515,15 +9518,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" ht="50.1" customHeight="1">
       <c r="A196" s="1" t="s">
-        <v>114</v>
+        <v>214</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>10</v>
+        <v>207</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D196" s="5">
         <v>2329</v>
@@ -9542,15 +9545,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" ht="50.1" customHeight="1">
       <c r="A197" s="1" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>10</v>
+        <v>207</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D197" s="288">
         <v>2513</v>
@@ -9569,15 +9572,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" ht="50.1" customHeight="1">
       <c r="A198" s="1" t="s">
-        <v>321</v>
+        <v>216</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>10</v>
+        <v>207</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D198" s="288">
         <v>2581</v>
@@ -9596,15 +9599,15 @@
         <v>24</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" ht="50.1" customHeight="1">
       <c r="A199" s="1" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D199" s="288">
         <v>2501</v>
@@ -9623,22 +9626,22 @@
         <v>224</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" ht="50.1" customHeight="1">
       <c r="A200" s="1" t="s">
-        <v>177</v>
+        <v>219</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D200" s="288">
         <v>2473</v>
       </c>
       <c r="E200" s="100"/>
       <c r="F200" s="1" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="G200" s="1">
         <v>245</v>
@@ -9650,15 +9653,15 @@
         <v>177</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" ht="50.1" customHeight="1">
       <c r="A201" s="1" t="s">
-        <v>328</v>
+        <v>221</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D201" s="288">
         <v>2413</v>
@@ -9677,15 +9680,15 @@
         <v>177</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" ht="50.1" customHeight="1">
       <c r="A202" s="1" t="s">
-        <v>65</v>
+        <v>222</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D202" s="288">
         <v>2243</v>
@@ -9704,15 +9707,15 @@
         <v>211</v>
       </c>
     </row>
-    <row r="203" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" ht="50.1" customHeight="1">
       <c r="A203" s="1" t="s">
-        <v>282</v>
+        <v>223</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D203" s="288">
         <v>2257</v>
@@ -9731,15 +9734,15 @@
         <v>157</v>
       </c>
     </row>
-    <row r="204" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" ht="50.1" customHeight="1">
       <c r="A204" s="1" t="s">
-        <v>71</v>
+        <v>224</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D204" s="288">
         <v>2256</v>
@@ -9758,15 +9761,15 @@
         <v>140</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" ht="50.1" customHeight="1">
       <c r="A205" s="1" t="s">
-        <v>23</v>
+        <v>225</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D205" s="288">
         <v>2223</v>
@@ -9785,15 +9788,15 @@
         <v>204</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" ht="50.1" customHeight="1">
       <c r="A206" s="1" t="s">
-        <v>327</v>
+        <v>226</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D206" s="288">
         <v>2374</v>
@@ -9812,15 +9815,15 @@
         <v>170</v>
       </c>
     </row>
-    <row r="207" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" ht="50.1" customHeight="1">
       <c r="A207" s="1" t="s">
-        <v>326</v>
+        <v>227</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D207" s="288">
         <v>2373</v>
@@ -9839,15 +9842,15 @@
         <v>185</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" ht="50.1" customHeight="1">
       <c r="A208" s="1" t="s">
-        <v>324</v>
+        <v>228</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D208" s="288">
         <v>2293</v>
@@ -9866,15 +9869,15 @@
         <v>185</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" ht="50.1" customHeight="1">
       <c r="A209" s="1" t="s">
-        <v>129</v>
+        <v>229</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D209" s="288">
         <v>2375</v>
@@ -9893,15 +9896,15 @@
         <v>185</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" ht="50.1" customHeight="1">
       <c r="A210" s="1" t="s">
-        <v>66</v>
+        <v>230</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D210" s="288">
         <v>2244</v>
@@ -9920,22 +9923,22 @@
         <v>151</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" ht="50.1" customHeight="1">
       <c r="A211" s="1" t="s">
-        <v>98</v>
+        <v>231</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D211" s="288">
         <v>2299</v>
       </c>
       <c r="E211" s="220"/>
       <c r="F211" s="1" t="s">
-        <v>325</v>
+        <v>232</v>
       </c>
       <c r="G211" s="1">
         <v>222</v>
@@ -9947,15 +9950,15 @@
         <v>172</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" ht="50.1" customHeight="1">
       <c r="A212" s="1" t="s">
-        <v>97</v>
+        <v>233</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D212" s="288">
         <v>2294</v>
@@ -9974,15 +9977,15 @@
         <v>111</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" ht="50.1" customHeight="1">
       <c r="A213" s="1" t="s">
-        <v>30</v>
+        <v>234</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D213" s="288">
         <v>2414</v>
@@ -10001,15 +10004,15 @@
         <v>111</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" ht="50.1" customHeight="1">
       <c r="A214" s="1" t="s">
-        <v>72</v>
+        <v>235</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D214" s="288">
         <v>2259</v>
@@ -10028,15 +10031,15 @@
         <v>181</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" ht="50.1" customHeight="1">
       <c r="A215" s="1" t="s">
-        <v>334</v>
+        <v>236</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D215" s="288">
         <v>2591</v>
@@ -10055,15 +10058,15 @@
         <v>168</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" ht="50.1" customHeight="1">
       <c r="A216" s="1" t="s">
-        <v>329</v>
+        <v>237</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D216" s="288">
         <v>2415</v>
@@ -10082,15 +10085,15 @@
         <v>161</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" ht="50.1" customHeight="1">
       <c r="A217" s="1" t="s">
-        <v>331</v>
+        <v>238</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D217" s="288">
         <v>2491</v>
@@ -10109,15 +10112,15 @@
         <v>150</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" ht="50.1" customHeight="1">
       <c r="A218" s="1" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D218" s="288">
         <v>2509</v>
@@ -10136,15 +10139,15 @@
         <v>114</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" ht="50.1" customHeight="1">
       <c r="A219" s="1" t="s">
-        <v>322</v>
+        <v>240</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D219" s="288">
         <v>2248</v>
@@ -10163,22 +10166,22 @@
         <v>127</v>
       </c>
     </row>
-    <row r="220" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" ht="50.1" customHeight="1">
       <c r="A220" s="1" t="s">
-        <v>155</v>
+        <v>241</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D220" s="288">
         <v>2432</v>
       </c>
       <c r="E220" s="240"/>
       <c r="F220" s="1" t="s">
-        <v>156</v>
+        <v>242</v>
       </c>
       <c r="G220" s="1">
         <v>237</v>
@@ -10190,15 +10193,15 @@
         <v>148</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" ht="50.1" customHeight="1">
       <c r="A221" s="1" t="s">
-        <v>74</v>
+        <v>243</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D221" s="288">
         <v>2261</v>
@@ -10217,15 +10220,15 @@
         <v>130</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" ht="50.1" customHeight="1">
       <c r="A222" s="1" t="s">
-        <v>73</v>
+        <v>244</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D222" s="288">
         <v>2260</v>
@@ -10244,15 +10247,15 @@
         <v>152</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" ht="50.1" customHeight="1">
       <c r="A223" s="1" t="s">
-        <v>335</v>
+        <v>245</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D223" s="288">
         <v>2611</v>
@@ -10271,15 +10274,15 @@
         <v>85</v>
       </c>
     </row>
-    <row r="224" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" ht="50.1" customHeight="1">
       <c r="A224" s="1" t="s">
-        <v>323</v>
+        <v>246</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D224" s="288">
         <v>2277</v>
@@ -10298,15 +10301,15 @@
         <v>70</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" ht="50.1" customHeight="1">
       <c r="A225" s="1" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D225" s="288">
         <v>2412</v>
@@ -10325,15 +10328,15 @@
         <v>103</v>
       </c>
     </row>
-    <row r="226" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" ht="50.1" customHeight="1">
       <c r="A226" s="1" t="s">
-        <v>330</v>
+        <v>248</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D226" s="288">
         <v>2416</v>
@@ -10352,15 +10355,15 @@
         <v>109</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" ht="50.1" customHeight="1">
       <c r="A227" s="1" t="s">
-        <v>333</v>
+        <v>249</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D227" s="288">
         <v>2590</v>
@@ -10379,15 +10382,15 @@
         <v>130</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" ht="50.1" customHeight="1">
       <c r="A228" s="1" t="s">
-        <v>194</v>
+        <v>250</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D228" s="288">
         <v>2494</v>
@@ -10406,15 +10409,15 @@
         <v>108</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" ht="50.1" customHeight="1">
       <c r="A229" s="1" t="s">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D229" s="288">
         <v>2499</v>
@@ -10433,15 +10436,15 @@
         <v>99</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" ht="50.1" customHeight="1">
       <c r="A230" s="1" t="s">
-        <v>197</v>
+        <v>252</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D230" s="288">
         <v>2500</v>
@@ -10460,15 +10463,15 @@
         <v>121</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" ht="50.1" customHeight="1">
       <c r="A231" s="1" t="s">
-        <v>198</v>
+        <v>253</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D231" s="288">
         <v>2504</v>
@@ -10487,15 +10490,15 @@
         <v>87</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" ht="50.1" customHeight="1">
       <c r="A232" s="1" t="s">
-        <v>196</v>
+        <v>254</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D232" s="288">
         <v>2497</v>
@@ -10514,15 +10517,15 @@
         <v>82</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" ht="50.1" customHeight="1">
       <c r="A233" s="1" t="s">
-        <v>332</v>
+        <v>255</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>12</v>
+        <v>218</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D233" s="288">
         <v>2498</v>
@@ -10541,15 +10544,15 @@
         <v>83</v>
       </c>
     </row>
-    <row r="234" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" ht="50.1" customHeight="1">
       <c r="A234" s="1" t="s">
-        <v>90</v>
+        <v>256</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>13</v>
+        <v>257</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D234" s="288">
         <v>2285</v>
@@ -10568,15 +10571,15 @@
         <v>228</v>
       </c>
     </row>
-    <row r="235" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" ht="50.1" customHeight="1">
       <c r="A235" s="1" t="s">
-        <v>336</v>
+        <v>258</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>13</v>
+        <v>257</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D235" s="288">
         <v>2276</v>
@@ -10595,15 +10598,15 @@
         <v>215</v>
       </c>
     </row>
-    <row r="236" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" ht="50.1" customHeight="1">
       <c r="A236" s="1" t="s">
-        <v>344</v>
+        <v>259</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>13</v>
+        <v>257</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D236" s="288">
         <v>2588</v>
@@ -10622,15 +10625,15 @@
         <v>223</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" ht="50.1" customHeight="1">
       <c r="A237" s="1" t="s">
-        <v>91</v>
+        <v>260</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>13</v>
+        <v>257</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D237" s="288">
         <v>2286</v>
@@ -10649,15 +10652,15 @@
         <v>211</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" ht="50.1" customHeight="1">
       <c r="A238" s="1" t="s">
-        <v>96</v>
+        <v>261</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>13</v>
+        <v>257</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D238" s="288">
         <v>2292</v>
@@ -10676,15 +10679,15 @@
         <v>192</v>
       </c>
     </row>
-    <row r="239" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" ht="50.1" customHeight="1">
       <c r="A239" s="1" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>13</v>
+        <v>257</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D239" s="288">
         <v>2287</v>
@@ -10703,15 +10706,15 @@
         <v>210</v>
       </c>
     </row>
-    <row r="240" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" ht="50.1" customHeight="1">
       <c r="A240" s="1" t="s">
-        <v>146</v>
+        <v>263</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>13</v>
+        <v>257</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D240" s="288">
         <v>2406</v>
@@ -10730,15 +10733,15 @@
         <v>177</v>
       </c>
     </row>
-    <row r="241" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" ht="50.1" customHeight="1">
       <c r="A241" s="1" t="s">
-        <v>93</v>
+        <v>264</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>13</v>
+        <v>257</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D241" s="288">
         <v>2288</v>
@@ -10757,15 +10760,15 @@
         <v>200</v>
       </c>
     </row>
-    <row r="242" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" ht="50.1" customHeight="1">
       <c r="A242" s="1" t="s">
-        <v>339</v>
+        <v>265</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>13</v>
+        <v>257</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D242" s="288">
         <v>2425</v>
@@ -10784,15 +10787,15 @@
         <v>200</v>
       </c>
     </row>
-    <row r="243" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" ht="50.1" customHeight="1">
       <c r="A243" s="1" t="s">
-        <v>338</v>
+        <v>266</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>13</v>
+        <v>257</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D243" s="288">
         <v>2424</v>
@@ -10811,15 +10814,15 @@
         <v>165</v>
       </c>
     </row>
-    <row r="244" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" ht="50.1" customHeight="1">
       <c r="A244" s="1" t="s">
-        <v>343</v>
+        <v>267</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>13</v>
+        <v>257</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D244" s="288">
         <v>2490</v>
@@ -10838,15 +10841,15 @@
         <v>119</v>
       </c>
     </row>
-    <row r="245" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" ht="50.1" customHeight="1">
       <c r="A245" s="1" t="s">
-        <v>340</v>
+        <v>268</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>13</v>
+        <v>257</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D245" s="288">
         <v>2426</v>
@@ -10865,15 +10868,15 @@
         <v>152</v>
       </c>
     </row>
-    <row r="246" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" ht="50.1" customHeight="1">
       <c r="A246" s="1" t="s">
-        <v>337</v>
+        <v>269</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>13</v>
+        <v>257</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D246" s="288">
         <v>2380</v>
@@ -10892,15 +10895,15 @@
         <v>115</v>
       </c>
     </row>
-    <row r="247" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" ht="50.1" customHeight="1">
       <c r="A247" s="1" t="s">
-        <v>151</v>
+        <v>270</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>13</v>
+        <v>257</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D247" s="288">
         <v>2422</v>
@@ -10919,15 +10922,15 @@
         <v>97</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" ht="50.1" customHeight="1">
       <c r="A248" s="1" t="s">
-        <v>342</v>
+        <v>271</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>13</v>
+        <v>257</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D248" s="288">
         <v>2430</v>
@@ -10946,15 +10949,15 @@
         <v>128</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" ht="50.1" customHeight="1">
       <c r="A249" s="1" t="s">
-        <v>24</v>
+        <v>272</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>13</v>
+        <v>257</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D249" s="288">
         <v>2254</v>
@@ -10973,15 +10976,15 @@
         <v>128</v>
       </c>
     </row>
-    <row r="250" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" ht="50.1" customHeight="1">
       <c r="A250" s="1" t="s">
-        <v>130</v>
+        <v>273</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>13</v>
+        <v>257</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D250" s="288">
         <v>2381</v>
@@ -11000,15 +11003,15 @@
         <v>107</v>
       </c>
     </row>
-    <row r="251" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" ht="50.1" customHeight="1">
       <c r="A251" s="1" t="s">
-        <v>153</v>
+        <v>274</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>13</v>
+        <v>257</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D251" s="288">
         <v>2429</v>
@@ -11027,15 +11030,15 @@
         <v>112</v>
       </c>
     </row>
-    <row r="252" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" ht="50.1" customHeight="1">
       <c r="A252" s="1" t="s">
-        <v>341</v>
+        <v>275</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>13</v>
+        <v>257</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D252" s="288">
         <v>2427</v>
@@ -11054,15 +11057,15 @@
         <v>106</v>
       </c>
     </row>
-    <row r="253" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" ht="50.1" customHeight="1">
       <c r="A253" s="1" t="s">
-        <v>152</v>
+        <v>276</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>13</v>
+        <v>257</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D253" s="288">
         <v>2428</v>
@@ -11081,15 +11084,15 @@
         <v>112</v>
       </c>
     </row>
-    <row r="254" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" ht="50.1" customHeight="1">
       <c r="A254" s="1" t="s">
-        <v>154</v>
+        <v>277</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>13</v>
+        <v>257</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D254" s="288">
         <v>2431</v>
@@ -11108,15 +11111,15 @@
         <v>110</v>
       </c>
     </row>
-    <row r="255" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" ht="50.1" customHeight="1">
       <c r="A255" s="1" t="s">
-        <v>348</v>
+        <v>278</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>13</v>
+        <v>257</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D255" s="288">
         <v>2736</v>
@@ -11135,15 +11138,15 @@
         <v>110</v>
       </c>
     </row>
-    <row r="256" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" ht="50.1" customHeight="1">
       <c r="A256" s="1" t="s">
-        <v>349</v>
+        <v>279</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>13</v>
+        <v>257</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D256" s="288">
         <v>2742</v>
@@ -11162,15 +11165,15 @@
         <v>112</v>
       </c>
     </row>
-    <row r="257" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" ht="50.1" customHeight="1">
       <c r="A257" s="1" t="s">
-        <v>347</v>
+        <v>280</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>13</v>
+        <v>257</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D257" s="288">
         <v>2628</v>
@@ -11189,15 +11192,15 @@
         <v>96</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" ht="50.1" customHeight="1">
       <c r="A258" s="1" t="s">
-        <v>345</v>
+        <v>281</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>13</v>
+        <v>257</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D258" s="288">
         <v>2600</v>
@@ -11216,15 +11219,15 @@
         <v>71</v>
       </c>
     </row>
-    <row r="259" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" ht="50.1" customHeight="1">
       <c r="A259" s="1" t="s">
-        <v>346</v>
+        <v>282</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>13</v>
+        <v>257</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D259" s="288">
         <v>2616</v>
@@ -11243,15 +11246,15 @@
         <v>63</v>
       </c>
     </row>
-    <row r="260" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" ht="50.1" customHeight="1">
       <c r="A260" s="1" t="s">
-        <v>355</v>
+        <v>283</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>11</v>
+        <v>284</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D260" s="288">
         <v>2508</v>
@@ -11270,15 +11273,15 @@
         <v>72</v>
       </c>
     </row>
-    <row r="261" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" ht="50.1" customHeight="1">
       <c r="A261" s="1" t="s">
-        <v>57</v>
+        <v>285</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>11</v>
+        <v>284</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D261" s="288">
         <v>2233</v>
@@ -11297,15 +11300,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="262" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" ht="50.1" customHeight="1">
       <c r="A262" s="1" t="s">
-        <v>352</v>
+        <v>286</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>11</v>
+        <v>284</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D262" s="288">
         <v>2420</v>
@@ -11324,15 +11327,15 @@
         <v>43</v>
       </c>
     </row>
-    <row r="263" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" ht="50.1" customHeight="1">
       <c r="A263" s="1" t="s">
-        <v>75</v>
+        <v>287</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>11</v>
+        <v>284</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D263" s="288">
         <v>2263</v>
@@ -11351,15 +11354,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="264" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" ht="50.1" customHeight="1">
       <c r="A264" s="1" t="s">
-        <v>354</v>
+        <v>288</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>11</v>
+        <v>284</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D264" s="288">
         <v>2505</v>
@@ -11378,15 +11381,15 @@
         <v>82</v>
       </c>
     </row>
-    <row r="265" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" ht="50.1" customHeight="1">
       <c r="A265" s="1" t="s">
-        <v>87</v>
+        <v>289</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>11</v>
+        <v>284</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D265" s="288">
         <v>2281</v>
@@ -11405,15 +11408,15 @@
         <v>58</v>
       </c>
     </row>
-    <row r="266" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" ht="50.1" customHeight="1">
       <c r="A266" s="1" t="s">
-        <v>25</v>
+        <v>290</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>11</v>
+        <v>284</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D266" s="288">
         <v>2378</v>
@@ -11432,15 +11435,15 @@
         <v>58</v>
       </c>
     </row>
-    <row r="267" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" ht="50.1" customHeight="1">
       <c r="A267" s="1" t="s">
-        <v>150</v>
+        <v>291</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>11</v>
+        <v>284</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D267" s="288">
         <v>2419</v>
@@ -11459,15 +11462,15 @@
         <v>58</v>
       </c>
     </row>
-    <row r="268" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" ht="50.1" customHeight="1">
       <c r="A268" s="1" t="s">
-        <v>47</v>
+        <v>292</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>11</v>
+        <v>284</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D268" s="288">
         <v>2219</v>
@@ -11486,15 +11489,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="269" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" ht="50.1" customHeight="1">
       <c r="A269" s="1" t="s">
-        <v>350</v>
+        <v>293</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>11</v>
+        <v>284</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D269" s="288">
         <v>2267</v>
@@ -11513,15 +11516,15 @@
         <v>59</v>
       </c>
     </row>
-    <row r="270" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" ht="50.1" customHeight="1">
       <c r="A270" s="1" t="s">
-        <v>199</v>
+        <v>294</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>11</v>
+        <v>284</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D270" s="288">
         <v>2507</v>
@@ -11540,15 +11543,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="271" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" ht="50.1" customHeight="1">
       <c r="A271" s="1" t="s">
-        <v>149</v>
+        <v>295</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>11</v>
+        <v>284</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D271" s="288">
         <v>2418</v>
@@ -11567,15 +11570,15 @@
         <v>42</v>
       </c>
     </row>
-    <row r="272" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" ht="50.1" customHeight="1">
       <c r="A272" s="1" t="s">
-        <v>176</v>
+        <v>296</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>11</v>
+        <v>284</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D272" s="288">
         <v>2472</v>
@@ -11594,15 +11597,15 @@
         <v>42</v>
       </c>
     </row>
-    <row r="273" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" ht="50.1" customHeight="1">
       <c r="A273" s="1" t="s">
-        <v>357</v>
+        <v>297</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>11</v>
+        <v>284</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D273" s="288">
         <v>2623</v>
@@ -11621,15 +11624,15 @@
         <v>42</v>
       </c>
     </row>
-    <row r="274" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" ht="50.1" customHeight="1">
       <c r="A274" s="1" t="s">
-        <v>81</v>
+        <v>298</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>11</v>
+        <v>284</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D274" s="288">
         <v>2270</v>
@@ -11648,15 +11651,15 @@
         <v>65</v>
       </c>
     </row>
-    <row r="275" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" ht="50.1" customHeight="1">
       <c r="A275" s="1" t="s">
-        <v>69</v>
+        <v>299</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>11</v>
+        <v>284</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D275" s="288">
         <v>2249</v>
@@ -11675,15 +11678,15 @@
         <v>63</v>
       </c>
     </row>
-    <row r="276" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" ht="50.1" customHeight="1">
       <c r="A276" s="1" t="s">
-        <v>353</v>
+        <v>300</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>11</v>
+        <v>284</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D276" s="288">
         <v>2421</v>
@@ -11702,15 +11705,15 @@
         <v>68</v>
       </c>
     </row>
-    <row r="277" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" ht="50.1" customHeight="1">
       <c r="A277" s="1" t="s">
-        <v>119</v>
+        <v>301</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>11</v>
+        <v>284</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D277" s="288">
         <v>2334</v>
@@ -11729,15 +11732,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="278" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" ht="50.1" customHeight="1">
       <c r="A278" s="1" t="s">
-        <v>227</v>
+        <v>302</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>11</v>
+        <v>284</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D278" s="288">
         <v>2608</v>
@@ -11756,15 +11759,15 @@
         <v>54</v>
       </c>
     </row>
-    <row r="279" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" ht="50.1" customHeight="1">
       <c r="A279" s="1" t="s">
-        <v>70</v>
+        <v>303</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>11</v>
+        <v>284</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D279" s="288">
         <v>2252</v>
@@ -11783,15 +11786,15 @@
         <v>64</v>
       </c>
     </row>
-    <row r="280" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" ht="50.1" customHeight="1">
       <c r="A280" s="1" t="s">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>11</v>
+        <v>284</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D280" s="288">
         <v>2268</v>
@@ -11810,15 +11813,15 @@
         <v>48</v>
       </c>
     </row>
-    <row r="281" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" ht="50.1" customHeight="1">
       <c r="A281" s="1" t="s">
-        <v>50</v>
+        <v>305</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>11</v>
+        <v>284</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D281" s="288">
         <v>2225</v>
@@ -11837,15 +11840,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="282" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" ht="50.1" customHeight="1">
       <c r="A282" s="1" t="s">
-        <v>356</v>
+        <v>306</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>11</v>
+        <v>284</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D282" s="288">
         <v>2622</v>
@@ -11864,15 +11867,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="283" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" ht="50.1" customHeight="1">
       <c r="A283" s="1" t="s">
-        <v>351</v>
+        <v>307</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>11</v>
+        <v>284</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D283" s="288">
         <v>2376</v>
@@ -11891,15 +11894,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="284" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" ht="50.1" customHeight="1">
       <c r="A284" s="1" t="s">
-        <v>195</v>
+        <v>308</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>11</v>
+        <v>284</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D284" s="288">
         <v>2496</v>
@@ -11918,15 +11921,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="285" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" ht="50.1" customHeight="1">
       <c r="A285" s="1" t="s">
-        <v>127</v>
+        <v>309</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D285" s="288">
         <v>2343</v>
@@ -11945,15 +11948,15 @@
         <v>176</v>
       </c>
     </row>
-    <row r="286" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" ht="48" customHeight="1">
       <c r="A286" s="1" t="s">
-        <v>366</v>
+        <v>310</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D286" s="288">
         <v>2604</v>
@@ -11972,15 +11975,15 @@
         <v>176</v>
       </c>
     </row>
-    <row r="287" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" ht="50.25" customHeight="1">
       <c r="A287" s="1" t="s">
-        <v>369</v>
+        <v>311</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D287" s="288">
         <v>2732</v>
@@ -11999,15 +12002,15 @@
         <v>162</v>
       </c>
     </row>
-    <row r="288" spans="1:9" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" ht="48.75" customHeight="1">
       <c r="A288" s="1" t="s">
-        <v>76</v>
+        <v>312</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D288" s="288">
         <v>2264</v>
@@ -12026,15 +12029,15 @@
         <v>162</v>
       </c>
     </row>
-    <row r="289" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" ht="50.1" customHeight="1">
       <c r="A289" s="1" t="s">
-        <v>360</v>
+        <v>313</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D289" s="288">
         <v>2557</v>
@@ -12053,15 +12056,15 @@
         <v>138</v>
       </c>
     </row>
-    <row r="290" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" ht="50.1" customHeight="1">
       <c r="A290" s="1" t="s">
-        <v>112</v>
+        <v>314</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D290" s="288">
         <v>2325</v>
@@ -12080,15 +12083,15 @@
         <v>89</v>
       </c>
     </row>
-    <row r="291" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" ht="50.1" customHeight="1">
       <c r="A291" s="1" t="s">
-        <v>113</v>
+        <v>315</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D291" s="288">
         <v>2326</v>
@@ -12107,15 +12110,15 @@
         <v>59</v>
       </c>
     </row>
-    <row r="292" spans="1:9" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" ht="48.75" customHeight="1">
       <c r="A292" s="1" t="s">
-        <v>364</v>
+        <v>316</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D292" s="288">
         <v>2596</v>
@@ -12134,15 +12137,15 @@
         <v>108</v>
       </c>
     </row>
-    <row r="293" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" ht="50.1" customHeight="1">
       <c r="A293" s="1" t="s">
-        <v>58</v>
+        <v>317</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D293" s="288">
         <v>2234</v>
@@ -12161,15 +12164,15 @@
         <v>104</v>
       </c>
     </row>
-    <row r="294" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" ht="50.1" customHeight="1">
       <c r="A294" s="1" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D294" s="288">
         <v>2235</v>
@@ -12188,15 +12191,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" ht="50.1" customHeight="1">
       <c r="A295" s="1" t="s">
-        <v>219</v>
+        <v>319</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D295" s="288">
         <v>2560</v>
@@ -12215,15 +12218,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="296" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" ht="48" customHeight="1">
       <c r="A296" s="1" t="s">
-        <v>169</v>
+        <v>320</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D296" s="288">
         <v>2462</v>
@@ -12242,15 +12245,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="297" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" ht="50.1" customHeight="1">
       <c r="A297" s="1" t="s">
-        <v>367</v>
+        <v>321</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D297" s="288">
         <v>2605</v>
@@ -12269,15 +12272,15 @@
         <v>104</v>
       </c>
     </row>
-    <row r="298" spans="1:9" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" ht="49.5" customHeight="1">
       <c r="A298" s="1" t="s">
-        <v>68</v>
+        <v>322</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D298" s="288">
         <v>2247</v>
@@ -12296,15 +12299,15 @@
         <v>140</v>
       </c>
     </row>
-    <row r="299" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" ht="50.1" customHeight="1">
       <c r="A299" s="1" t="s">
-        <v>147</v>
+        <v>323</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D299" s="288">
         <v>2408</v>
@@ -12323,15 +12326,15 @@
         <v>48</v>
       </c>
     </row>
-    <row r="300" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" ht="50.1" customHeight="1">
       <c r="A300" s="1" t="s">
-        <v>64</v>
+        <v>324</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D300" s="288">
         <v>2242</v>
@@ -12350,15 +12353,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" ht="50.1" customHeight="1">
       <c r="A301" s="1" t="s">
-        <v>45</v>
+        <v>325</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D301" s="288">
         <v>2216</v>
@@ -12377,15 +12380,15 @@
         <v>59</v>
       </c>
     </row>
-    <row r="302" spans="1:9" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" ht="48.75" customHeight="1">
       <c r="A302" s="1" t="s">
-        <v>368</v>
+        <v>326</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D302" s="288">
         <v>2626</v>
@@ -12404,15 +12407,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="303" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" ht="45" customHeight="1">
       <c r="A303" s="1" t="s">
-        <v>173</v>
+        <v>327</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D303" s="288">
         <v>2466</v>
@@ -12431,15 +12434,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" ht="50.1" customHeight="1">
       <c r="A304" s="1" t="s">
-        <v>172</v>
+        <v>328</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D304" s="288">
         <v>2465</v>
@@ -12458,15 +12461,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="305" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" ht="48" customHeight="1">
       <c r="A305" s="1" t="s">
-        <v>361</v>
+        <v>329</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D305" s="288">
         <v>2558</v>
@@ -12485,15 +12488,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="306" spans="1:9" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" ht="48.75" customHeight="1">
       <c r="A306" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D306" s="288">
         <v>2396</v>
@@ -12512,15 +12515,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:9" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" ht="48.75" customHeight="1">
       <c r="A307" s="1" t="s">
-        <v>116</v>
+        <v>331</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D307" s="288">
         <v>2331</v>
@@ -12539,15 +12542,15 @@
         <v>24</v>
       </c>
     </row>
-    <row r="308" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" ht="50.1" customHeight="1">
       <c r="A308" s="1" t="s">
-        <v>170</v>
+        <v>332</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D308" s="288">
         <v>2463</v>
@@ -12566,15 +12569,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" ht="50.1" customHeight="1">
       <c r="A309" s="1" t="s">
-        <v>117</v>
+        <v>333</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D309" s="288">
         <v>2332</v>
@@ -12593,15 +12596,15 @@
         <v>93</v>
       </c>
     </row>
-    <row r="310" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" ht="50.1" customHeight="1">
       <c r="A310" s="1" t="s">
-        <v>26</v>
+        <v>334</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D310" s="288">
         <v>2213</v>
@@ -12620,15 +12623,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="311" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" ht="48" customHeight="1">
       <c r="A311" s="1" t="s">
-        <v>171</v>
+        <v>335</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D311" s="288">
         <v>2464</v>
@@ -12647,15 +12650,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="312" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" ht="50.1" customHeight="1">
       <c r="A312" s="1" t="s">
-        <v>148</v>
+        <v>336</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D312" s="288">
         <v>2409</v>
@@ -12674,15 +12677,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="313" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" ht="50.1" customHeight="1">
       <c r="A313" s="1" t="s">
-        <v>225</v>
+        <v>337</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D313" s="288">
         <v>2606</v>
@@ -12701,15 +12704,15 @@
         <v>78</v>
       </c>
     </row>
-    <row r="314" spans="1:9" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" ht="49.5" customHeight="1">
       <c r="A314" s="1" t="s">
-        <v>363</v>
+        <v>338</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D314" s="288">
         <v>2586</v>
@@ -12728,15 +12731,15 @@
         <v>29</v>
       </c>
     </row>
-    <row r="315" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" ht="50.1" customHeight="1">
       <c r="A315" s="1" t="s">
-        <v>175</v>
+        <v>339</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D315" s="288">
         <v>2471</v>
@@ -12755,15 +12758,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" ht="50.1" customHeight="1">
       <c r="A316" s="1" t="s">
-        <v>220</v>
+        <v>340</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D316" s="288">
         <v>2561</v>
@@ -12782,15 +12785,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" ht="50.1" customHeight="1">
       <c r="A317" s="1" t="s">
-        <v>36</v>
+        <v>341</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D317" s="288">
         <v>2201</v>
@@ -12809,15 +12812,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="318" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" ht="50.1" customHeight="1">
       <c r="A318" s="1" t="s">
-        <v>43</v>
+        <v>342</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D318" s="288">
         <v>2212</v>
@@ -12836,15 +12839,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" ht="50.1" customHeight="1">
       <c r="A319" s="1" t="s">
-        <v>218</v>
+        <v>343</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D319" s="288">
         <v>2556</v>
@@ -12863,15 +12866,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" ht="45.75" customHeight="1">
       <c r="A320" s="1" t="s">
-        <v>118</v>
+        <v>344</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D320" s="288">
         <v>2333</v>
@@ -12890,15 +12893,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="321" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" ht="50.1" customHeight="1">
       <c r="A321" s="1" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D321" s="288">
         <v>2562</v>
@@ -12917,15 +12920,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="322" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" ht="50.1" customHeight="1">
       <c r="A322" s="1" t="s">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>239</v>
+        <v>11</v>
       </c>
       <c r="D322" s="288">
         <v>2602</v>
@@ -12945,7 +12948,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="3RUHiy+L98XjWzzRDnrGgWitaZWe9EEwjv3YWuipLFFQQeTtQkYPjkp3h9ZlgRv575UKE/aQAB/Uihgb088KpA==" saltValue="O6/f4iDIjPVe7NbPAr0EWg==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection sort="0" autoFilter="0"/>
   <protectedRanges>
     <protectedRange sqref="A1:I322" name="AllowSortFilter"/>
   </protectedRanges>
@@ -12956,8 +12959,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DD3BB65-B8DB-4602-BF4F-F090D54436C7}">
-  <dimension ref="A1:I36"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O36"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" style="1" customWidth="1"/>
@@ -12965,14 +12968,14 @@
     <col min="4" max="4" width="19.7109375" style="301" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="17.7109375" style="1" customWidth="1"/>
-    <col min="7" max="9" width="8.85546875" style="1"/>
-    <col min="10" max="10" width="20.7109375" style="1" customWidth="1"/>
-    <col min="11" max="14" width="8.85546875" style="1"/>
-    <col min="15" max="15" width="50.7109375" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.85546875" style="1"/>
+    <col min="7" max="9" width="8.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" style="1" hidden="1" customWidth="1"/>
+    <col min="11" max="14" width="8.85546875" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="50.7109375" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.85546875" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="2" customFormat="1" ht="50.1" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -12986,30 +12989,30 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:9" ht="50.1" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>158</v>
+        <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="D2" s="301">
         <v>5734</v>
@@ -13028,15 +13031,15 @@
         <v>228</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="50.1" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>206</v>
+        <v>348</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="D3" s="301">
         <v>5829</v>
@@ -13055,15 +13058,15 @@
         <v>204</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="50.1" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>207</v>
+        <v>349</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="D4" s="301">
         <v>5836</v>
@@ -13082,15 +13085,15 @@
         <v>148</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="50.1" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>235</v>
+        <v>350</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="D5" s="301">
         <v>9105</v>
@@ -13109,15 +13112,15 @@
         <v>146</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="50.1" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>160</v>
+        <v>54</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="D6" s="301">
         <v>5738</v>
@@ -13136,15 +13139,15 @@
         <v>159</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="50.1" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>134</v>
+        <v>60</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="D7" s="301">
         <v>5686</v>
@@ -13163,15 +13166,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="50.1" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>101</v>
+        <v>351</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="D8" s="301">
         <v>5603</v>
@@ -13190,15 +13193,15 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="50.1" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>204</v>
+        <v>352</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="D9" s="301">
         <v>5824</v>
@@ -13217,15 +13220,15 @@
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="50.1" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>135</v>
+        <v>353</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="D10" s="301">
         <v>5687</v>
@@ -13244,15 +13247,15 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="50.1" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>44</v>
+        <v>354</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="D11" s="301">
         <v>5515</v>
@@ -13271,15 +13274,15 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="50.1" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>221</v>
+        <v>355</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="D12" s="301">
         <v>5870</v>
@@ -13298,15 +13301,15 @@
         <v>117</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="50.1" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>49</v>
+        <v>356</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="D13" s="301">
         <v>5524</v>
@@ -13325,15 +13328,15 @@
         <v>92</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="50.1" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>357</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="D14" s="301">
         <v>5551</v>
@@ -13352,15 +13355,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="50.1" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="D15" s="301">
         <v>5637</v>
@@ -13379,15 +13382,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="50.1" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="D16" s="301">
         <v>5705</v>
@@ -13406,15 +13409,15 @@
         <v>214</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="50.1" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>144</v>
+        <v>358</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="D17" s="301">
         <v>5704</v>
@@ -13433,15 +13436,15 @@
         <v>195</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="50.1" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>237</v>
+        <v>359</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="D18" s="301">
         <v>9117</v>
@@ -13460,22 +13463,22 @@
         <v>113</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="50.1" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>236</v>
+        <v>360</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="D19" s="301">
         <v>9111</v>
       </c>
       <c r="E19" s="58"/>
       <c r="F19" s="1" t="s">
-        <v>18</v>
+        <v>361</v>
       </c>
       <c r="G19" s="1">
         <v>99</v>
@@ -13487,22 +13490,22 @@
         <v>104</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="50.1" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>77</v>
+        <v>362</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="D20" s="301">
         <v>5565</v>
       </c>
       <c r="E20" s="137"/>
       <c r="F20" s="1" t="s">
-        <v>78</v>
+        <v>363</v>
       </c>
       <c r="G20" s="1">
         <v>111</v>
@@ -13514,15 +13517,15 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="50.1" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>238</v>
+        <v>364</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="D21" s="301">
         <v>9121</v>
@@ -13541,15 +13544,15 @@
         <v>124</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="50.1" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>110</v>
+        <v>365</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="D22" s="301">
         <v>5621</v>
@@ -13568,15 +13571,15 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="50.1" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>201</v>
+        <v>366</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="D23" s="301">
         <v>5814</v>
@@ -13595,15 +13598,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="50.1" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>162</v>
+        <v>367</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="D24" s="301">
         <v>5745</v>
@@ -13622,15 +13625,15 @@
         <v>143</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="50.1" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>234</v>
+        <v>368</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="D25" s="301">
         <v>9092</v>
@@ -13649,15 +13652,15 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="50.1" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>163</v>
+        <v>369</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="D26" s="301">
         <v>5746</v>
@@ -13676,15 +13679,15 @@
         <v>126</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="50.1" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>174</v>
+        <v>370</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>10</v>
+        <v>207</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="D27" s="301">
         <v>5769</v>
@@ -13703,15 +13706,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="50.1" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>59</v>
+        <v>210</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>10</v>
+        <v>207</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="D28" s="301">
         <v>5536</v>
@@ -13730,15 +13733,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="50.1" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>79</v>
+        <v>371</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>11</v>
+        <v>284</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>37</v>
+        <v>347</v>
       </c>
       <c r="D29" s="301">
         <v>5566</v>
@@ -13757,19 +13760,240 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:9" ht="50.1" hidden="1" customHeight="1"/>
+    <row r="31" spans="1:9" ht="50.1" hidden="1" customHeight="1"/>
+    <row r="32" spans="1:9" ht="50.1" hidden="1" customHeight="1"/>
+    <row r="33" ht="50.1" hidden="1" customHeight="1"/>
+    <row r="34" ht="50.1" hidden="1" customHeight="1"/>
+    <row r="35" ht="50.1" hidden="1" customHeight="1"/>
+    <row r="36" ht="50.1" hidden="1" customHeight="1"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="JZTYxGIGvJ/niyScjsrO4ueprLFwt2MfadjJXVyUfattmzNc67ogPJ42iIF+l5mLqSAHyXzp+8MGMGqIP64vxg==" saltValue="HkdmmJtzdOwYMXjFoLXGnA==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection sort="0" autoFilter="0"/>
   <protectedRanges>
     <protectedRange sqref="A1:I29" name="AllowSortFilter"/>
   </protectedRanges>
   <autoFilter ref="A1:I29" xr:uid="{3DD3BB65-B8DB-4602-BF4F-F090D54436C7}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea7a09a4-fe73-437e-8a86-996460e9b058">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A1C7DD37AE641E4B9B3FD2F75B2D99BC" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6b9cb41f595aff4764e09aef2b23c1ed">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ea7a09a4-fe73-437e-8a86-996460e9b058" xmlns:ns3="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="daad8a4a6daff5298e6b89d91afce8e3" ns2:_="" ns3:_="">
+    <xsd:import namespace="ea7a09a4-fe73-437e-8a86-996460e9b058"/>
+    <xsd:import namespace="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ea7a09a4-fe73-437e-8a86-996460e9b058" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="d2f5926c-fefe-46c4-85d9-9ef0eea46f5c" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{6fbb2a74-2168-4404-a595-59f9a11d4eed}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A4264F6-F1B2-4C1F-AC3E-E4A4F6ADA4C1}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A9C02D4-8006-454F-846F-34B4CD8BADE7}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CCD9C5E-3E74-405D-8A4E-9623DB6E3A4F}"/>
 </file>